--- a/02_Literature_Review/Literature_Review_Matrix.xlsx
+++ b/02_Literature_Review/Literature_Review_Matrix.xlsx
@@ -3,12 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Literature_Matrix" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Search_Log" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Litmaps_Discovery_Screening" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P001_Extraction" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P002_Extraction" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +39,28 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF17365D"/>
       <sz val="11"/>
     </font>
     <font>
@@ -63,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -76,6 +100,20 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -454,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AD20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.42578125" customWidth="1" style="2" min="1" max="1"/>
@@ -484,7 +522,8 @@
     <col width="19.85546875" customWidth="1" style="2" min="26" max="26"/>
     <col width="9.140625" customWidth="1" style="2" min="27" max="29"/>
     <col width="27.7109375" customWidth="1" style="2" min="30" max="30"/>
-    <col width="9.140625" customWidth="1" style="2" min="31" max="16384"/>
+    <col width="9.140625" customWidth="1" style="2" min="31" max="31"/>
+    <col width="9.140625" customWidth="1" style="2" min="32" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
@@ -660,89 +699,119 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Remote Sensing</t>
+          <t>Remote Sensing (MDPI), 10(5), Article 689</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Teknaf, Cox's Bazar, Bangladesh</t>
+          <t>Teknaf Peninsula, Cox's Bazar, Bangladesh; Kutupalong–Balukhali, Unchiprang, and Nayapara–Leda camp zones</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Classification: 30 Dec 2016 (pre-influx) vs 15 Dec 2017 (post-influx). NDVI: 6 Dec 2015, 30 Dec 2016, 8 Feb 2017, and 15 Dec 2017. Field survey: 28 Dec 2017.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sentinel-2A/2B 10 m bands 2, 3, 4, 8; QuickBird 2010 pan-sharpened to 0.6 m; SRTM 30 m; GPS/spatial-video field samples; Google Earth; BBS, ISCG, IOM, UNHCR/OCHA refugee and population data; 2011 roads/physical features.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Random Forest land-cover classification in RStudio using 16 predictors (13 spectral/index variables and elevation, slope, aspect), 1000 trees and mtry 5–6; six initial classes merged to forest/nonforest/camp; OOB and independent accuracy assessment; ring-buffer, conversion-matrix, and NDVI change analysis.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Camp area increased by 1,356 ha across the three sites, while net forest cover declined by 2,283 ha and nonforest increased by 928 ha from Dec 2016 to Dec 2017. Kutupalong–Balukhali expanded from 146 to 1,365 ha (+835%) and lost 2,060 ha of forest. Nayapara–Leda lost 176 ha and Unchiprang lost 47 ha. NDVI declines were strongest west and southwest of Kutupalong–Balukhali.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
+          <t>Yes — quantified net forest decline of 2,283 ha across three camp zones; site-level and directional conversion estimates reported.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>No — fragmentation and elephant-corridor impacts were discussed, but no patch, edge, core-area, or connectivity metrics were calculated.</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>No — carbon storage implications were discussed, but biomass or carbon loss was not estimated.</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>ML: Yes — Random Forest classification and variable-importance ranking. XAI: No — no SHAP or comparable explainability framework.</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>No — descriptive two-date pre/post change analysis without matched controls, counterfactual estimation, or causal identification.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Author-stated: persistent cloud cover restricted analysis to dry-season images; no high-resolution Google Earth image was available for 2017; moderate-resolution imagery could miss remote settlements beneath tree shade; homestead vegetation was sometimes classified as forest. Additional: only two classification dates, simplified three-class outcomes, static buffers, and no probability-sample area adjustment.</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Provides a high-accuracy short-term benchmark, but not a 2001–2025 annual trajectory, causal counterfactual, fragmentation metrics, biomass/carbon accounting, time-varying camp exposure, spatially validated driver model, SHAP interpretation, or integrated conservation-priority assessment.</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/rs10050689</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>02_Literature_Review\Research_Papers\01_Direct_Rohingya_Forest_Studies\2018_hassan_rohingya_refugee_crisis_forest_cover_change.pdf</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>MDPI; VTechWorks; Litmaps</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>DOI 10.3390/rs10050689 and official publisher/repository metadata</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>Official metadata and full text verified; methods, findings, accuracy, limitations, and research gap extracted</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>Open-access full text downloaded and reviewed</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>Peer-reviewed journal article</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>No/Not assessed yet</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>10.3390/rs10050689</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>Not downloaded yet</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>Litmaps</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>Exact paper title</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>Title and metadata screened</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>Open-access full text available</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>Journal Article</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>13 July 2026</t>
@@ -750,7 +819,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>Foundational direct Rohingya forest-cover study; full-text extraction pending</t>
+          <t>Published 30 April 2018 under CC BY. Overall accuracies: 94.53% (2016) and 95.14% (2017); Kappa: 0.93 and 0.94. Foundational direct study; descriptive rather than causally identified.</t>
         </is>
       </c>
     </row>
@@ -775,32 +844,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>World Bank</t>
+          <t>World Bank Policy Research Working Paper No. 9948</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cox's Bazar District, Bangladesh</t>
+          <t>Cox's Bazar District, Bangladesh; official Rohingya camp boundaries and surrounding treatment and control buffers.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2010, 2014, 2017 and 2020</t>
+          <t>LULC years: 2010, 2014, February 2017 and February 2020. Pre-treatment: 2010, 2014 and 2017. Post-treatment: 2020.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Landsat imagery; camp boundaries; spatial land-use/land-cover data</t>
+          <t>Landsat imagery at 30 m; official camp boundaries; Protected Planet protected-area data; WorldPop population; VIIRS nightlights; road-distance data; 10,000 sampled pixels.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Remote-sensing LULC analysis and Difference-in-Differences</t>
+          <t>Random Forest land-cover classification, NDVI, post-classification change analysis, and linear-probability Difference-in-Differences with pixel and year fixed effects. Treatment: 0–5 km from camp boundaries. Control: 10–15 km from camp boundaries.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Forest/grassland declined by 12,807.99 ha across Cox's Bazar between 2017 and 2020. Within official camp boundaries, approximately 1,337 ha of forest was lost. DiD attributed an additional 2,653.7 ha of forest loss to camp establishment in the 0–5 km treatment zone (~1,082.4 ha within 0–1 km and ~1,571.3 ha within 1–5 km).</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -820,64 +889,74 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>ML: Yes — Random Forest classification; XAI: No</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Yes — Difference-in-Differences</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Only four classified years and one post-treatment observation; 30 m spatial resolution; static distance-based treatment; possible spillover into control areas; baseline imbalance between treatment and control zones; no spatially clustered errors; no fragmentation, carbon, SHAP or uncertainty propagation.</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>The study provides an important causal benchmark but does not offer a 2001–2025 annual panel, time-varying camp exposure, SDID weighting, fragmentation outcomes, above-ground carbon attribution, explainable driver analysis or conservation-priority mapping.</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>10.1596/1813-9450-9948</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>02_Literature_Review\Research_Papers\01_Direct_Rohingya_Forest_Studies\2022_dampha_rohingya_camps_forest_loss.pdf</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Litmaps citation network</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Citation connection from Hassan et al. (2018)</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Title, metadata and abstract screened</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Official full text downloaded and reviewed</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Policy Research Working Paper</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Yes — Difference-in-Differences</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>World Bank Policy Research Working Paper 9948</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Not downloaded yet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Litmaps citation network</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Citation connection from Hassan et al. (2018)</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Title, metadata and abstract screened</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Open-access full text available</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Policy Research Working Paper</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>No / Not confirmed as peer-reviewed</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>13 July 2026</t>
@@ -885,7 +964,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Existing causal forest-loss study; full methodological extraction pending</t>
+          <t>Principal existing causal benchmark for Rohingya-related forest loss. Settlement-area DiD narrative contains an internal numerical inconsistency; forest attributable-loss figure (2,653.7 ha) is internally consistent.</t>
         </is>
       </c>
     </row>
@@ -1686,6 +1765,1491 @@
       <c r="AD9" t="inlineStr">
         <is>
           <t>PDF dated 11 November 2025; author's current CV lists it as a 2026 working paper under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Langer, S.; Tiede, D.; Lüthje, F.</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2015</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Long-term Monitoring of the Environmental Impact of a Refugee Camp Based on Landsat Time Series: The Example of Deforestation and Reforestation During the Whole Lifespan of the Camp Lukole, Tanzania</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>GI_Forum 2015, Volume 3 / Journal for Geographic Information Science</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lukole refugee camp, Tanzania</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>10.1553/giscience2015s434</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Not downloaded yet</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Related-paper discovery; first batch screening</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Title and abstract screened</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Methodological reference; restoration. Methodological reference; study area is Lukole refugee camp, Tanzania, not Bangladesh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hasan, M. E.; Zhang, L.; Dewan, A.; Guo, H.; Mahmood, R.</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Spatiotemporal Pattern of Forest Degradation and Loss of Ecosystem Function Associated with Rohingya Influx: A Geospatial Approach</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Land Degradation &amp; Development</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Cox's Bazar–Teknaf Peninsula, Bangladesh</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Not verified</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>10.1002/ldr.3821</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Not downloaded yet</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Related-paper discovery; first batch screening</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Title and abstract screened</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Direct forest change. Core empirical study; publication metadata should be verified during full-text collection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sarkar, S. K.; Saroar, M. M.; Chakraborty, T.</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Navigating Nature's Toll: Assessing the Ecological Impact of the Refugee Crisis in Cox's Bazar, Bangladesh</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Heliyon</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Cox's Bazar, Bangladesh</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>10.1016/j.heliyon.2023.e18255</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Not downloaded yet</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Related-paper discovery; first batch screening</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Title and abstract screened</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Direct ecological/forest impact. Core empirical evidence for ecological impact and ecosystem-service-value change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sarkar, S. K.; Saroar, M.; Chakraborty, T.</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cost of Ecosystem Service Value Due to Rohingya Refugee Influx in Bangladesh</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Disaster Medicine and Public Health Preparedness</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ukhiya and Teknaf, Cox's Bazar, Bangladesh</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>ANN classification used; XAI not identified</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>10.1017/dmp.2022.125</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Not downloaded yet</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Related-paper discovery; first batch screening</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Title and abstract screened</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Direct forest change; ecosystem services. Litmaps may show 2022; version-of-record appears in the 2023 journal volume. Verify final citation during full-text extraction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ahmed, F.; Alam, S.; Saha, O. R.; Rahman, A.</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>The Rohingya Refugee Crisis in Bangladesh: Assessing the Impact on Land Use Patterns and Land Surface Temperature Using Machine Learning</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Environmental Monitoring &amp; Assessment</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rohingya camp areas, Cox's Bazar, Bangladesh</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>10.1007/s10661-024-12701-3</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Not downloaded yet</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Related-paper discovery; first batch screening</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Title and abstract screened</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Machine learning; forest/LULC. Important comparator for the proposed predictive ML component; SHAP and spatial validation must be checked from full text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Gromny, E.; Jenerowicz-Sanikowska, M.; Haarpaintner, J.; et al. (13 authors)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Remote Sensing Insights into Land Cover Dynamics and Socio-Economic Drivers: The Case of Mtendeli Refugee Camp, Tanzania (2016–2022)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Remote Sensing Applications: Society and Environment</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mtendeli refugee camp, Tanzania</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>10.1016/j.rsase.2024.101334</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Not downloaded yet</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Related-paper discovery; first batch screening</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Title and abstract screened</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Transferable remote-sensing methodology. Methodological comparator from Mtendeli camp, Tanzania; not direct evidence for Cox's Bazar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mohiuddin, M.; Hossain, M.; Islam, M. Y.; Nowreen, S.; Sultana, N.</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Assessing the Impact of Land Use Land Cover Change after Rohingya Forced Migration on Elephant Route in Cox's Bazar District, Bangladesh</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Landscape and Ecological Engineering</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Cox's Bazar district, Bangladesh</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>10.1007/s11355-025-00642-z</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Not downloaded yet</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Related-paper discovery; first batch screening</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Title and abstract screened</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Conservation; elephant corridor. Important for wildlife-corridor, connectivity and conservation-priority analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Chowdhury, F. I.; Bhuiyan, R. H.; Espelta, J. M.; Resco de Dios, V.; Dilshad, T.; Haque, M. R.; Aman, M. G.; Lloret, F.</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Land-Use Legacies and Tree Species Richness Affect Short-Term Resilience in Reforested Areas of the World's Largest Refugee Camp</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ecological Engineering</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kutupalong reforested areas, Cox's Bazar, Bangladesh</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>No — restoration-focused</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>10.1016/j.ecoleng.2025.107612</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Not downloaded yet</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Related-paper discovery; first batch screening</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Title and abstract screened</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Restoration and resilience. Restoration-focused rather than deforestation-attribution study.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Liu, J.; Zevenbergen, C.; Lu, J.; Qi, Q.; Veerbeek, W.; Chowdhury, S. W.; Qian, L.</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Land-Use Governance of Borderland Protected Areas Under Refugee Expansion and Climate Threats: Evidence from Teknaf, Bangladesh</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Teknaf, Bangladesh</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>10.3390/land15061024</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Not downloaded yet</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Related-paper discovery; first batch screening</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Title and abstract screened</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Protected-area governance. Very recent study; important for protected-area governance and policy recommendations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sobczak-Szelc, K.; Chułek, M.; Espegren, A.; Malak, M. A.; Jenerowicz-Sanikowska, M.; Quader, M. A.</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Exploring the Role of Common-Pool Resources and MalCoping in Socio-Environmental Dynamics: A Case Study of the Kutupalong Refugee Camp, Bangladesh</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Journal of Immigrant &amp;amp; Refugee Studies</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kutupalong refugee camp, Bangladesh</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>10.1080/15562948.2025.2607538</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Not downloaded yet</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Related-paper discovery; first batch screening</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Title and abstract screened</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Background and environmental drivers. Contextual and qualitative study; not a remote-sensing or causal forest-loss analysis. Verify final publication year during citation checking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rashid, K. J.; Hoque, M. A.; Esha, T. A.; Rahman, M. A.; Paul, A.</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Spatiotemporal changes of vegetation and land surface temperature in the refugee camps and its surrounding areas of Bangladesh after the Rohingya influx from Myanmar</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Environment, Development and Sustainability</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rohingya refugee camps and surrounding areas, Cox's Bazar, Bangladesh</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Full-text extraction pending</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Yes — vegetation-cover change</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>No/Not verified</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>ML/classification use to verify</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>10.1007/s10668-020-00733-x</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Not downloaded yet</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Citation-network recommendation already present in the Litmap</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Title, metadata and abstract screened</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Access to verify</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Relevant vegetation and LST study; detailed methodological extraction pending.</t>
         </is>
       </c>
     </row>
@@ -1700,7 +3264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.42578125" customWidth="1" style="2" min="1" max="1"/>
@@ -1708,7 +3272,8 @@
     <col width="37.7109375" customWidth="1" style="2" min="4" max="4"/>
     <col width="18" customWidth="1" style="2" min="5" max="7"/>
     <col width="44" customWidth="1" style="2" min="8" max="8"/>
-    <col width="9.140625" customWidth="1" style="2" min="9" max="16384"/>
+    <col width="9.140625" customWidth="1" style="2" min="9" max="9"/>
+    <col width="9.140625" customWidth="1" style="2" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2073,7 +3638,43 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>First ten outlined recommendations screened: all Include (P009–P018 pending Litmap addition)</t>
+          <t>All ten first-batch recommendations were included: eight as direct or contextual Cox's Bazar studies and two as transferable refugee-camp methodological references.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Reconciliation of previously saved Rashid et al. article</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Rashid et al. (2021) was already saved in the Litmap but was not included in the master literature matrix; assigned C011 and P019.</t>
         </is>
       </c>
     </row>
@@ -2088,1024 +3689,1942 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="1" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Candidate ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Author-Year Label</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Exact Title</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Authors</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Journal/Source</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>DOI or URL</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Connected Seed Papers</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Abstract Available</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Preliminary Theme</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Title Relevance</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Abstract Relevance</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Screening Decision</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Inclusion Reason</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Exclusion Reason</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Added to Litmap</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Final Paper ID</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Date Screened</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Langer, 2015</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Long-term Monitoring of the Environmental Impact of a Refugee Camp Based on Landsat Time Series: The Example of Deforestation and Reforestation During the Whole Lifespan of the Camp Lukole, Tanzania</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Langer, S.; Tiede, D.; Lüthje, F.</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>GI_Forum 2015, Volume 3 / Journal for Geographic Information Science</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>10.1553/giscience2015s434</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Hassan 2023 clearly visible; additional connections to verify</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Conservation and Restoration</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Provides a transferable long-term Landsat time-series framework for assessing deforestation and reforestation across the complete lifecycle of a refugee camp.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Methodological reference; study area is Lukole refugee camp, Tanzania, not Bangladesh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Hasan, 2020</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Spatiotemporal Pattern of Forest Degradation and Loss of Ecosystem Function Associated with Rohingya Influx: A Geospatial Approach</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Hasan, M. E.; Zhang, L.; Dewan, A.; Guo, H.; Mahmood, R.</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Land Degradation &amp; Development</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>10.1002/ldr.3821</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Multiple seed connections — exact connection unclear</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Direct Forest Change</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Directly examines spatiotemporal forest degradation and loss of ecosystem function associated with the Rohingya influx using geospatial analysis.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Core empirical study; publication metadata should be verified during full-text collection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sarkar, 2023</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Navigating Nature's Toll: Assessing the Ecological Impact of the Refugee Crisis in Cox's Bazar, Bangladesh</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sarkar, S. K.; Saroar, M. M.; Chakraborty, T.</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Heliyon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>10.1016/j.heliyon.2023.e18255</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Multiple seed connections — exact connection unclear</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Direct Forest Change</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Directly assesses forest, settlement and ecological-service changes associated with the Rohingya refugee crisis in Cox's Bazar.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Core empirical evidence for ecological impact and ecosystem-service-value change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sarkar, 2022</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cost of Ecosystem Service Value Due to Rohingya Refugee Influx in Bangladesh</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sarkar, S. K.; Saroar, M.; Chakraborty, T.</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Disaster Medicine and Public Health Preparedness</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>10.1017/dmp.2022.125</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Multiple seed connections — exact connection unclear</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Direct Forest Change</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Estimates land-cover change and the economic cost of ecosystem-service loss associated with the Rohingya influx in Ukhiya and Teknaf.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Litmaps may show 2022; version-of-record appears in the 2023 journal volume. Verify final citation during full-text extraction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ahmed, 2024</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>The Rohingya Refugee Crisis in Bangladesh: Assessing the Impact on Land Use Patterns and Land Surface Temperature Using Machine Learning</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ahmed, F.; Alam, S.; Saha, O. R.; Rahman, A.</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Environmental Monitoring &amp; Assessment</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10.1007/s10661-024-12701-3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Multiple seed connections — exact connection unclear</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Direct Rohingya-camp study combining machine learning, land-use analysis and land-surface-temperature assessment.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Important comparator for the proposed predictive ML component; SHAP and spatial validation must be checked from full text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Gromny, 2024</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Remote Sensing Insights into Land Cover Dynamics and Socio-Economic Drivers: The Case of Mtendeli Refugee Camp, Tanzania (2016–2022)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Gromny, E.; Jenerowicz-Sanikowska, M.; Haarpaintner, J.; et al. (13 authors)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Remote Sensing Applications: Society and Environment</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>10.1016/j.rsase.2024.101334</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Multiple seed connections — exact connection unclear</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Direct Forest Change</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Provides a recent transferable remote-sensing design for analysing land-cover dynamics and socioeconomic drivers around a refugee camp.</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>P014</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Methodological comparator from Mtendeli camp, Tanzania; not direct evidence for Cox's Bazar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>C007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mohiuddin, 2025</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Assessing the Impact of Land Use Land Cover Change after Rohingya Forced Migration on Elephant Route in Cox's Bazar District, Bangladesh</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mohiuddin, M.; Hossain, M.; Islam, M. Y.; Nowreen, S.; Sultana, N.</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Landscape and Ecological Engineering</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>10.1007/s11355-025-00642-z</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Multiple seed connections — exact connection unclear</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Conservation and Restoration</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Directly evaluates Rohingya-related LULC change and its impact on elephant movement routes in Cox's Bazar.</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>P015</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Important for wildlife-corridor, connectivity and conservation-priority analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Chowdhury, 2025</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Land-Use Legacies and Tree Species Richness Affect Short-Term Resilience in Reforested Areas of the World's Largest Refugee Camp</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Chowdhury, F. I.; Bhuiyan, R. H.; Espelta, J. M.; Resco de Dios, V.; Dilshad, T.; Haque, M. R.; Aman, M. G.; Lloret, F.</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ecological Engineering</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>10.1016/j.ecoleng.2025.107612</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Hassan connection visible; additional connections to verify</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Conservation and Restoration</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Evaluates reforestation recovery and resilience in Kutupalong, supporting the restoration and conservation-priority component.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>P016</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Restoration-focused rather than deforestation-attribution study.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>C009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Liu, 2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Land-Use Governance of Borderland Protected Areas Under Refugee Expansion and Climate Threats: Evidence from Teknaf, Bangladesh</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Liu, J.; Zevenbergen, C.; Lu, J.; Qi, Q.; Veerbeek, W.; Chowdhury, S. W.; Qian, L.</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>10.3390/land15061024</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Multiple seed connections — exact connection unclear</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Conservation and Restoration</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Directly addresses land-use governance, protected areas, refugee expansion and climate pressure in Teknaf.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>P017</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Very recent study; important for protected-area governance and policy recommendations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>C010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sobczak-Szelc, 2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Exploring the Role of Common-Pool Resources and MalCoping in Socio-Environmental Dynamics: A Case Study of the Kutupalong Refugee Camp, Bangladesh</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sobczak-Szelc, K.; Chułek, M.; Espegren, A.; Malak, M. A.; Jenerowicz-Sanikowska, M.; Quader, M. A.</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Journal of Immigrant &amp;amp; Refugee Studies</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>10.1080/15562948.2025.2607538</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sarkar connection visible; additional connections to verify</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Background or Context</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Provides qualitative evidence on common-pool resources, coping behaviour and socio-environmental pressures in Kutupalong, supporting interpretation of forest-loss drivers and policy responses.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Contextual and qualitative study; not a remote-sensing or causal forest-loss analysis. Verify final publication year during citation checking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rashid, 2021</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Spatiotemporal changes of vegetation and land surface temperature in the refugee camps and its surrounding areas of Bangladesh after the Rohingya influx from Myanmar</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rashid, K. J.; Hoque, M. A.; Esha, T. A.; Rahman, M. A.; Paul, A.</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Environment, Development and Sustainability</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>10.1007/s10668-020-00733-x</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Already present in Litmap citation network</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Direct Forest Change</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Directly analyses post-influx vegetation and land-surface-temperature changes in the Rohingya camp landscape and surrounding areas.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Article was already present in the Litmap but had not been assigned a master-matrix ID. Online publication occurred in 2020; journal issue year retained as 2021.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Candidate ID</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Author-Year Label</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Exact Title</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Authors</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Journal/Source</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>DOI or URL</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Connected Seed Papers</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Abstract Available</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>Preliminary Theme</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>Title Relevance</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>Abstract Relevance</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>Screening Decision</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>Inclusion Reason</t>
-        </is>
-      </c>
-      <c r="O1" s="4" t="inlineStr">
-        <is>
-          <t>Exclusion Reason</t>
-        </is>
-      </c>
-      <c r="P1" s="4" t="inlineStr">
-        <is>
-          <t>Added to Litmap</t>
-        </is>
-      </c>
-      <c r="Q1" s="4" t="inlineStr">
-        <is>
-          <t>Final Paper ID</t>
-        </is>
-      </c>
-      <c r="R1" s="4" t="inlineStr">
-        <is>
-          <t>Date Screened</t>
-        </is>
-      </c>
-      <c r="S1" s="4" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>P001 — Full-Text Extraction</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="n"/>
+      <c r="C1" s="6" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Verified extraction</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Primary source / location</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Verified citation</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Hassan, M. M., Smith, A. C., Walker, K., Rahman, M. K., &amp; Southworth, J. (2018). Rohingya refugee crisis and forest cover change in Teknaf, Bangladesh. Remote Sensing, 10(5), 689. https://doi.org/10.3390/rs10050689</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>MDPI version of record</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Publication status</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Peer-reviewed, open-access journal article; received 6 March 2018, accepted 25 April 2018, published 30 April 2018; CC BY.</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Article p. 1; MDPI metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Research objective</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Quantify the rapid expansion of Rohingya refugee settlements and associated forest-cover destruction around the three largest camp concentrations before and after the August 2017 influx.</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Abstract; Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Study area</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Teknaf Peninsula (555 km²), focusing on Kutupalong–Balukhali, Unchiprang, and Nayapara–Leda. Study buffers were 10 km, 3 km, and 4 km, respectively.</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Section 2.1; Table 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Classification period</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>30 December 2016 (pre-influx) and 15 December 2017 (post-influx).</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Section 2.2; Figure 3; Table 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>NDVI dates</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>6 December 2015, 30 December 2016, 8 February 2017, and 15 December 2017; dry-season dates were selected to reduce cloud and phenological variability.</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Table 2; Section 2.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Primary satellite data</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Sentinel-2A/2B, 10 m, bands 2, 3, 4 and 8. QuickBird 2010 was pan-sharpened to 0.6 m for pre-influx interpretation/validation. SRTM 30 m supplied elevation, slope and aspect.</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Section 2.2; Table 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Reference and ancillary data</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Approximately 200 GPS/spatial-video field samples plus 300 stratified random reference samples; about 500 manually interpreted 2016 samples; Google Earth/QuickBird; BBS population data; ISCG/IOM/UNHCR/OCHA refugee data; 2011 master-plan roads and physical features.</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Section 2.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Preprocessing</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Visible and NIR bands were stacked and subset to the study boundary. QuickBird multispectral bands were pan-sharpened. NDVI and other spectral transforms were calculated; land-cover outputs were later converted to polygons in ArcGIS.</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Section 2.2–2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Initial land-cover classes</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Forest, urban, camp, water, agriculture, and sand; later merged to forest, nonforest, and camp for change analysis.</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Section 2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Predictors</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>16 predictors: elevation, slope, aspect; Sentinel visible/NIR reflectance; NDVI, MSI, SAVI; tasseled-cap greenness, brightness and wetness; PCA scores 1–3.</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Section 2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Random Forest settings</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>RStudio implementation; 1,000 trees; 5–6 of 16 variables randomly selected at each split; complete predictor set retained.</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Section 2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>70/30 bootstrap/OOB design plus independent cross-validation. Authors report 150 stratified validation points per period; for the 2017 map they describe 50 reference points per class because later high-resolution Google Earth imagery was unavailable.</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Section 3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Overall accuracy: 94.53% (2016), 95.14% (2017). Kappa: 0.93, 0.94. OOB error: 3.67, 3.19. Forest producer accuracy: 92.98–98.21%; forest user accuracy: 96.49–92.98%.</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Section 3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Important variables</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>NIR and red bands, NDVI, elevation, and tasseled-cap greenness/brightness were most important; slope and aspect were least important.</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Section 3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Aggregate change</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Across the three camp zones: camp +1,356 ha; forest −2,283 ha; nonforest +928 ha between December 2016 and December 2017.</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Table 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Kutupalong–Balukhali</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Camp: 146→1,365 ha (+1,219 ha; +835%). Forest: 11,800→9,740 ha (−2,060 ha; −18%). Nonforest: +842 ha. Major losses occurred south, west and southwest.</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Section 3.2; Table 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Kutupalong conversion</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Forest→nonforest: 1,882 ha; forest→camp: 763 ha; nonforest→camp: 536 ha. Southwest alone contained 605 ha of camp expansion and 940 ha of forest degradation.</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Section 3.2; Figure 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Nayapara–Leda</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Camp: 29→133 ha (+105 ha; +359%). Forest: 2,860→2,684 ha (−176 ha; −6%). Nonforest: +71 ha.</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Section 3.3; Table 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Unchiprang</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Camp: 0→32 ha. Forest: 1,499→1,452 ha (−47 ha; −3%). Nonforest: +15 ha. The paper also reports detailed conversion flows within the 3 km buffer.</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Section 3.3; Table 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>NDVI result</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Vegetation greenness/health declined significantly after the influx within roughly 7 km southwest and 4 km west of Kutupalong–Balukhali.</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Figure 6; Section 3.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Authors' interpretation</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Rapid camp expansion and associated fuelwood, timber and subsistence pressure converted forested hills, affected protected forest and elephant habitat, and increased landslide and wildlife-conflict risk.</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Discussion and Conclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Author-stated limitations</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Cloud cover forced use of December dry-season imagery; images closer to the influx date were unavailable. Post-influx high-resolution Google Earth imagery was unavailable. Moderate-resolution data missed some settlements under tree shade, and some homestead vegetation was classified as forest.</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Discussion</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Critical limitations for our study</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Only two classification dates and no long-term annual trajectory; no matched control or counterfactual; no formal causal identification; no fragmentation metrics; no biomass/carbon quantification; simplified classes and static buffers; no spatial block validation or area-adjusted change uncertainty.</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Critical appraisal</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Relevance to proposed research</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Foundational benchmark for direct Rohingya-related forest-change mapping. It validates the feasibility of Sentinel-2 + RF + field reference data and provides early quantified loss estimates, while clearly motivating our long-term, carbon, fragmentation, XAI and causal extensions.</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Research synthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Research gap derived</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Extend from a 2016–2017 descriptive snapshot to a 2001–2025 annual record; estimate causal additional loss using SDID; quantify fragmentation and above-ground carbon loss; use lagged, time-varying exposure predictors, spatial validation, SHAP and conservation-priority mapping.</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Research synthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>How it will be cited</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Background: earliest high-resolution evidence of rapid post-influx forest conversion. Literature review: benchmark direct study using RF. Gap: short-term descriptive design without carbon, fragmentation or causal counterfactual.</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Planned manuscript use</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Important figures/tables</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Table 1 (camp buffers/populations); Figure 2 (study area); Figure 3 (pre/post imagery); Table 2 (data inventory); Figure 5 (classified maps); Table 3 (area changes); Figure 6 (NDVI profiles); Figure 7 (conversion map); Figure 8 (field photographs).</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Article figures and tables</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Direct quotations</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>No direct quotations retained; all evidence has been paraphrased to support synthesis and avoid unnecessary verbatim reuse.</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Extraction policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Official article</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mdpi.com/2072-4292/10/5/689</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/rs10050689</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Persistent identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Downloaded PDF</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>02_Literature_Review\Research_Papers\01_Direct_Rohingya_Forest_Studies\2018_hassan_rohingya_refugee_crisis_forest_cover_change.pdf</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>VTechWorks archived open-access copy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Verified Extraction</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Source/Page</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Langer, 2015</t>
+          <t>Treatment definition</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>0–5 km geodesic distance from nearest official post-2017 camp boundary</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Long-term Monitoring of the Environmental Impact of a Refugee Camp Based on Landsat Time Series: The Example of Deforestation and Reforestation During the Whole Lifespan of the Camp Lukole, Tanzania</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Langer, S.; Tiede, D.; Lüthje, F.</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>GI_Forum 2015, Volume 3 / Journal for Geographic Information Science</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>10.1553/giscience2015s434</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Hassan 2023 clearly visible; additional connections to verify</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Conservation and Restoration</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Provides a transferable long-term Landsat time-series framework for assessing deforestation and reforestation across the complete lifecycle of a refugee camp.</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>No — pending addition</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>P009</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>13 July 2026</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Methodological reference; study area is Lukole refugee camp, Tanzania, not Bangladesh.</t>
+          <t>§5.2; Table 1 note</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Hasan, 2020</t>
+          <t>Control definition</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>10–15 km from nearest camp boundary</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spatiotemporal Pattern of Forest Degradation and Loss of Ecosystem Function Associated with Rohingya Influx: A Geospatial Approach</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Hasan, M. E.; Zhang, L.; Dewan, A.; Guo, H.; Mahmood, R.</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Land Degradation &amp; Development</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>10.1002/ldr.3821</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Multiple seed connections — exact connection unclear</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Direct Forest Change</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Directly examines spatiotemporal forest degradation and loss of ecosystem function associated with the Rohingya influx using geospatial analysis.</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>No — pending addition</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>P010</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>13 July 2026</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Core empirical study; publication metadata should be verified during full-text collection.</t>
+          <t>§5.2; Table 1 note</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Sarkar, 2023</t>
+          <t>Selected years</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>LULC: 2010, 2014, Feb 2017, Feb 2020; population 2010–2020; nightlights 2014–2020</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Navigating Nature's Toll: Assessing the Ecological Impact of the Refugee Crisis in Cox's Bazar, Bangladesh</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Sarkar, S. K.; Saroar, M. M.; Chakraborty, T.</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Heliyon</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>10.1016/j.heliyon.2023.e18255</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Multiple seed connections — exact connection unclear</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Direct Forest Change</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Directly assesses forest, settlement and ecological-service changes associated with the Rohingya refugee crisis in Cox's Bazar.</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>No — pending addition</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>P011</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>13 July 2026</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Core empirical evidence for ecological impact and ecosystem-service-value change.</t>
+          <t>§4–5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Sarkar, 2022</t>
+          <t>RF classification</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Six LULC classes; RF outperformed MLE and SVM in ArcGIS Pro supervised classification</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cost of Ecosystem Service Value Due to Rohingya Refugee Influx in Bangladesh</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Sarkar, S. K.; Saroar, M.; Chakraborty, T.</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2022</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Disaster Medicine and Public Health Preparedness</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>10.1017/dmp.2022.125</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Multiple seed connections — exact connection unclear</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Direct Forest Change</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Estimates land-cover change and the economic cost of ecosystem-service loss associated with the Rohingya influx in Ukhiya and Teknaf.</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>No — pending addition</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>P012</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>13 July 2026</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Litmaps may show 2022; version-of-record appears in the 2023 journal volume. Verify final citation during full-text extraction.</t>
+          <t>§5.1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ahmed, 2024</t>
+          <t>DiD model</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Linear probability DiD with pixel and year FE (Eq. 1); continuous DiD for population/nightlights (Eq. 2)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The Rohingya Refugee Crisis in Bangladesh: Assessing the Impact on Land Use Patterns and Land Surface Temperature Using Machine Learning</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Ahmed, F.; Alam, S.; Saha, O. R.; Rahman, A.</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Environmental Monitoring &amp; Assessment</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>10.1007/s10661-024-12701-3</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Multiple seed connections — exact connection unclear</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Machine Learning</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Direct Rohingya-camp study combining machine learning, land-use analysis and land-surface-temperature assessment.</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>No — pending addition</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>P013</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>13 July 2026</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Important comparator for the proposed predictive ML component; SHAP and spatial validation must be checked from full text.</t>
+          <t>§5.2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Gromny, 2024</t>
+          <t>Placebo tests</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Forest/settlement placebos for 2014 and 2017 (drop 2020); population/nightlights placebos for 2015 and 2016</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote Sensing Insights into Land Cover Dynamics and Socio-Economic Drivers: The Case of Mtendeli Refugee Camp, Tanzania (2016–2022)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Gromny, E.; Jenerowicz-Sanikowska, M.; Haarpaintner, J.; et al. (13 authors)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Remote Sensing Applications: Society and Environment</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>10.1016/j.rsase.2024.101334</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Multiple seed connections — exact connection unclear</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Direct Forest Change</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Provides a recent transferable remote-sensing design for analysing land-cover dynamics and socioeconomic drivers around a refugee camp.</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>No — pending addition</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>P014</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>13 July 2026</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Methodological comparator from Mtendeli camp, Tanzania; not direct evidence for Cox's Bazar.</t>
+          <t>§5.2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Mohiuddin, 2025</t>
+          <t>0–1 km exclusion test</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Omitting 0–1 km pixels reduces forest DiD from 7.6 pp to 4.5 pp (still significant)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Assessing the Impact of Land Use Land Cover Change after Rohingya Forced Migration on Elephant Route in Cox's Bazar District, Bangladesh</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Mohiuddin, M.; Hossain, M.; Islam, M. Y.; Nowreen, S.; Sultana, N.</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Landscape and Ecological Engineering</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>10.1007/s11355-025-00642-z</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Multiple seed connections — exact connection unclear</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Conservation and Restoration</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Directly evaluates Rohingya-related LULC change and its impact on elephant movement routes in Cox's Bazar.</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>No — pending addition</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>P015</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>13 July 2026</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Important for wildlife-corridor, connectivity and conservation-priority analysis.</t>
+          <t>§5.3; Fig. 7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Chowdhury, 2025</t>
+          <t>Protected-area analysis</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Heterogeneity by protected vs non-protected pixels; losses concentrated outside protected areas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Land-Use Legacies and Tree Species Richness Affect Short-Term Resilience in Reforested Areas of the World's Largest Refugee Camp</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Chowdhury, F. I.; Bhuiyan, R. H.; Espelta, J. M.; Resco de Dios, V.; Dilshad, T.; Haque, M. R.; Aman, M. G.; Lloret, F.</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Ecological Engineering</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>10.1016/j.ecoleng.2025.107612</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Hassan connection visible; additional connections to verify</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Conservation and Restoration</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Evaluates reforestation recovery and resilience in Kutupalong, supporting the restoration and conservation-priority component.</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>No — pending addition</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>P016</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>13 July 2026</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Restoration-focused rather than deforestation-attribution study.</t>
+          <t>§5.4; results</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Liu, 2026</t>
+          <t>Attributable forest loss</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>≈2,653.7 ha additional forest loss in 0–5 km treatment vs counterfactual; ~1,082.4 ha in 0–1 km and ~1,571.3 ha in 1–5 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Land-Use Governance of Borderland Protected Areas Under Refugee Expansion and Climate Threats: Evidence from Teknaf, Bangladesh</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Liu, J.; Zevenbergen, C.; Lu, J.; Qi, Q.; Veerbeek, W.; Chowdhury, S. W.; Qian, L.</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Land</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>10.3390/land15061024</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Multiple seed connections — exact connection unclear</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Conservation and Restoration</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Directly addresses land-use governance, protected areas, refugee expansion and climate pressure in Teknaf.</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>No — pending addition</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>P017</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>13 July 2026</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Very recent study; important for protected-area governance and policy recommendations.</t>
+          <t>§6.2; fn. 14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Sobczak-Szelc, 2026</t>
+          <t>District descriptive loss</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Forest/grassland −12,807.99 ha (−19.57%) from 2017 to 2020; camp-interior forest loss ≈1,337 ha</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Exploring the Role of Common-Pool Resources and MalCoping in Socio-Environmental Dynamics: A Case Study of the Kutupalong Refugee Camp, Bangladesh</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Sobczak-Szelc, K.; Chułek, M.; Espegren, A.; Malak, M. A.; Jenerowicz-Sanikowska, M.; Quader, M. A.</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Journal of Immigrant &amp;amp; Refugee Studies</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>10.1080/15562948.2025.2607538</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sarkar connection visible; additional connections to verify</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Background or Context</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Provides qualitative evidence on common-pool resources, coping behaviour and socio-environmental pressures in Kutupalong, supporting interpretation of forest-loss drivers and policy responses.</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>No — pending addition</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>P018</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>13 July 2026</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Contextual and qualitative study; not a remote-sensing or causal forest-loss analysis. Verify final publication year during citation checking.</t>
+          <t>Table 2; §6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Limitations</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Four LULC dates; one post year; 30 m Landsat; static buffers; possible spillover; no clustered SEs; appendices on request</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>§5–7; our appraisal</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Research gap</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>No annual long panel, time-varying exposure, SDID, fragmentation, carbon, XAI, or conservation-priority mapping</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Our appraisal</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Numerical inconsistency</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Settlement conversion narrative reports 7,681.9 ha then calculates 4,539.3 ha in footnote arithmetic</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>§6.2; fn. 15</t>
         </is>
       </c>
     </row>

--- a/02_Literature_Review/Literature_Review_Matrix.xlsx
+++ b/02_Literature_Review/Literature_Review_Matrix.xlsx
@@ -11,6 +11,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Litmaps_Discovery_Screening" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P001_Extraction" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P002_Extraction" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P005_Extraction" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P006_Extraction" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P007_Extraction" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P008_Extraction" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P009_Extraction" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P010_Extraction" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P011_Extraction" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P012_Extraction" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P013_Extraction" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P014_Extraction" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -20,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +74,11 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
@@ -87,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -115,6 +130,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -522,8 +538,8 @@
     <col width="19.85546875" customWidth="1" style="2" min="26" max="26"/>
     <col width="9.140625" customWidth="1" style="2" min="27" max="29"/>
     <col width="27.7109375" customWidth="1" style="2" min="30" max="30"/>
-    <col width="9.140625" customWidth="1" style="2" min="31" max="31"/>
-    <col width="9.140625" customWidth="1" style="2" min="32" max="16384"/>
+    <col width="9.140625" customWidth="1" style="2" min="31" max="32"/>
+    <col width="9.140625" customWidth="1" style="2" min="33" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
@@ -1119,7 +1135,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>An Integrated Machine Learning and Remote Sensing Approach for Monitoring Forest Degradation Due to Rohingya Refugee Influx in Bangladesh</t>
+          <t>An integrated machine learning and remote sensing approach for monitoring forest degradation due to Rohingya refugee influx in Bangladesh</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1129,94 +1145,114 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ukhiya–Teknaf, Cox's Bazar</t>
+          <t>Cox's Bazar District, Bangladesh, with particular emphasis on Teknaf and Ukhia, where the largest Rohingya camp concentrations are located.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2013–2019; prediction to 2030</t>
+          <t>Historical LULC comparison includes imagery representing approximately 1990, 1991, 2013 and 2020. Vegetation-degradation result reported for 2013–2019. Prediction horizon: 2030. Exact image dates require full-text verification.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Multi-temporal satellite imagery and geospatial land-use/land-cover data. Exact satellite sensors, bands, resolutions, training samples and validation datasets could not be verified without full text.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Remote sensing, LULC indices, Random Forest</t>
+          <t>Three land-use/land-cover change indices were used to monitor vegetation degradation. The study compared Maximum Likelihood Classification, Support Vector Machine, Random Forest and Artificial Neural Network approaches. Random Forest was used to identify degradation patterns around refugee-camp concentrations and support land-use prediction to 2030. Exact model settings and prediction procedure remain pending.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Deep vegetation decreased by approximately 74.28 km² between 2013 and 2019. The decline in deep vegetation was accompanied by an increase in shallow vegetation. Teknaf and Ukhia experienced the highest levels of forest degradation among the analysed areas. The projected land-use pattern suggests an increase of approximately 150.92 km² in shallow vegetation near refugee camps between 2013 and 2030.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>Yes — deep vegetation decline and forest degradation analysed</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>No — no formal fragmentation metrics verified</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>ML: Yes — MLC, SVM, RF and ANN considered; Random Forest highlighted in the reported results. XAI: No — SHAP or another explainability method not reported</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>No — observational monitoring and prediction; no counterfactual causal design</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Full text was unavailable, so satellite sensors, image dates, classification accuracy, training-validation strategy, model hyperparameters, land-cover indices and prediction procedure could not be independently verified. The study reports associations between refugee-camp locations and vegetation degradation but does not implement a causal counterfactual design. It does not quantify fragmentation, biomass/carbon loss or prediction uncertainty and does not use explainable AI.</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>The study demonstrates the value of combining remote sensing with machine learning for forest-degradation monitoring and prediction, but it does not provide a continuous 2001–2025 annual forest-loss panel, formal fragmentation outcomes, above-ground carbon attribution, SHAP-based driver analysis, spatially robust validation or SDID-based causal attribution.</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>10.1016/j.rsase.2022.100696</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Full text not downloaded — paid publisher access</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>DOI or exact title</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Metadata and abstract screened</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Publisher metadata, abstract and section snippets reviewed; full text unavailable due to paid access</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>ML: Yes; XAI: Not verified</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>10.1016/j.rsase.2022.100696</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Not downloaded yet</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Litmaps</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>DOI or exact title</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Metadata and abstract screened</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Journal Article</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>13 July 2026</t>
@@ -1224,7 +1260,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Direct comparator for the proposed ML analysis</t>
+          <t>Partial extraction only. Accessible sources report imagery for 1990, 1991, 2013 and 2020, while the abstract reports the main vegetation change for 2013–2019. Exact temporal construction must be checked if the full article becomes available. Publisher record: Volume 25, Article 100696, January 2022.</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1272,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mahmood, H.; Saha, C.; Saha, S.</t>
+          <t>Mahmood, H. (Hossain Mahmood); Saha, C.; Saha, S.</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1244,7 +1280,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tracking Forest Recovery: Early Biomass and Carbon Stock Monitoring in the Rohingya Refugee Camps, Cox's Bazar, Bangladesh</t>
+          <t>Tracking forest recovery: Early biomass and carbon stock monitoring in the Rohingya Refugee camps, Cox's Bazar, Bangladesh</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1254,32 +1290,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Restored forest sites in and around the Rohingya refugee camps, Cox's Bazar</t>
+          <t>Restored forest sites within and around the Rohingya refugee camp landscape, Cox's Bazar South Forest Division, Bangladesh. Restoration context: approximately 3,200 ha of reserved forest were reported as damaged following the Rohingya influx. Forest-restoration activities began in 2019 across approximately 292 ha of degraded forest land.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Restoration from 2019; field inventory during 2024 (Table 4). Exact fieldwork month/day not stated.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Field vegetation and biomass measurements; detailed extraction pending</t>
+          <t>Field-based vegetation, biomass, litter, dead-wood, root and soil-carbon measurements from restored forest sites (34 sampled blocks &gt;0.5 ha across 14 camps + 2 denuded controls). Plot design: 10×10 m main plots with nested 1×1 m subplots and 0.5×0.5×0.5 m root pits. Inventory year 2024.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Biomass and carbon-stock assessment using field measurements and allometric relationships; detailed extraction pending</t>
+          <t>Field inventory of restored vegetation and multiple carbon pools; tree AGB via hill-zone species-specific/common allometries (GoB 2019; Mahmood et al. 2019a); root biomass by pit method; C from 50% biomass (trees) or 50% LOI at 450 °C (other pools); soil C to 30 cm with core bulk density (0–15 and 15–30 cm). Stand allometric models: Ln(Y)=1.30+1.11 Ln(BA/ha) for AGB and Ln(Y)=0.61+1.11 Ln(BA/ha) for AGC (adj. R² 0.98; Rmse 0.18). SAS University Edition.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Mean AGB 33.34±5.76 t/ha; mean root BGB 2.26±0.32 t/ha. Total C across five pools 8.84–149.86 t/ha (mean 93.90±4.85); soil C to 30 cm dominant (mean pool values: AGB+undergrowth C 16.37; litter 0.15; DWD 0.11; root 1.03; soil 76.29 t/ha). Results report 24 planted + 10 naturally regenerated species (abstract states 34+14; Table 3 lists 33 species) — inconsistency noted. Publisher highlights swap AGB/BGB means relative to abstract/Table 6.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>No — restoration-focused</t>
+          <t>Indirect context only — the study focuses on restoration, not historical forest-loss mapping</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1289,69 +1325,79 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>Yes — biomass and five carbon pools quantified</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>No — field-based observational restoration assessment</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>No historical/attributable carbon-loss accounting; DBH threshold unspecified; species-count and Highlights AGB/BGB inconsistencies; model n/external validation unclear; disturbance-affected plantations; soil C only to 30 cm.</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>The study quantifies biomass and carbon stocks in restored sites, but does not estimate annual historical biomass loss, carbon loss from deforestation, CO2-equivalent emissions, spatially explicit carbon change, or the proportion causally attributable to the post-2017 refugee influx. The proposed research will integrate annual forest-loss maps with spatial biomass data and SDID estimates to quantify attributable above-ground carbon loss.</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Very High — Biomass and Carbon</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>10.1016/j.envc.2024.101063</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>02_Literature_Review\Research_Papers\03_Biomass_Carbon_Studies\2025_mahmood_tracking_forest_recovery_biomass_carbon.pdf</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>DOI or exact title</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Title, metadata and abstract screened</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Open-access full text downloaded and reviewed</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Research Article</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>10.1016/j.envc.2024.101063</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Not downloaded yet</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Litmaps</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>DOI or exact title</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Title, metadata and abstract screened</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Open-access full text available</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Journal Article</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>13 July 2026</t>
@@ -1359,7 +1405,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Important local biomass and carbon reference; focuses on restoration stock rather than historical or influx-attributable carbon loss. Litmaps displays the node as "Hossain, 2024". The publisher version of record is Environmental Challenges, Volume 18, April 2025, Article 101063. The DOI is identical: 10.1016/j.envc.2024.101063. Publication year retained as 2025. Publisher page: https://www.sciencedirect.com/science/article/pii/S2667010024002294</t>
+          <t>VoR year 2025 (Vol. 18, April 2025); copyright 2024. First author full name Hossain Mahmood (Litmaps may label Hossain 2024). Critical: restoration stocks ≠ influx-attributable historical carbon loss. Extraction notes: P005_2025_mahmood_extraction_notes.docx</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1425,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Landscape Fragmentation and Population Distribution in Refugee Camps: Evidence from the Rohingya Refugee Influx in Bangladesh</t>
+          <t>Landscape fragmentation and population distribution in refugee camps: evidence from the Rohingya refugee influx in Bangladesh</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1389,104 +1435,114 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rohingya refugee camp landscape, Cox's Bazar, Bangladesh</t>
+          <t>Approximately 2,500 ha covering 34 Rohingya refugee camps in Ukhia and Teknaf, Cox's Bazar District. Camp clusters include Kutupalong–Balukhali, Nayapara and scattered camps including Camps 14, 15, 16, 21, 22 and 23. The study considered the 34 Cox's Bazar camps and excluded Bhasan Char.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Pre-influx image: 30 November 2016; post-influx image: 3 January 2024; comparison period 2016–2024.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sentinel-2 and population/spatial data; detailed extraction pending</t>
+          <t>Sentinel-2A imagery; Humanitarian Response camp-boundary shapefile; UNHCR 2024 camp-level population data; high-resolution Google Earth Engine reference imagery. Sentinel-2A images dated 30 November 2016 and 3 January 2024; classification in Google Earth Engine. Bands B2, B3, B4, B8 at 10 m; WGS 1984 UTM Zone 46N; winter dry-season imagery.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Land-cover classification and landscape-fragmentation metrics; detailed extraction pending</t>
+          <t>Random Forest LULC classification in GEE (200 trees; sqrt(mtry); ~2,000 samples/image, ~80/20 train/validation). Post-classification categorical change detection (ArcGIS Pro Change Detection Wizard). FRAGSTATS 4.2 fragmentation (Queen 8-neighbour) with seven class-level and two landscape-level metrics. NDVI from Bands 4 and 8. Camp-level population mapping from UNHCR 2024 settlement areas; bivariate correlation of % forest vs % settlement change (settlement change as population proxy).</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Forest 1,688.8 → 767.3 ha (−54.6%); settlement 144.8 → 1,011.5 ha (+598.5%). Conversions to settlement: 695.2 ha forest, 205.1 ha agriculture/open field, 19.4 ha water (919.7 ha total). Forest NP 663→2,468; PD 26.6→98.9; AI 91.9→75.2; COHESION 99.6→96.4; DIVISION 0.7996→0.9968. Landscape NP 7,724→12,917; PD 309.4→517.5. Correlation r=−0.73 (p&lt;0.05). Camp 15: ~57,922 people, +67.1 ha settlement, ~62.8–62.9 ha forest loss. Restoration signals at Kutupalong RC, Nayapara RC, Camps 23–25.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>Yes — quantified 2016–2024 forest decline and conversions</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Yes — seven class metrics and two landscape metrics</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ML: Yes — Random Forest classification; XAI: No</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>No — descriptive pre/post analysis and bivariate correlation</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Only two image dates were analysed, so annual trajectories, intermediate disturbances and restoration timing were not observed. The study area was restricted mainly to official camp boundaries, rather than the wider camp-influenced forest landscape. The correlation analysis cannot establish causal attribution. Settlement change was used as a proxy for population change because historic camp-level population data were unavailable. Fragmentation metrics are scale-sensitive and depend on the 10 m classification resolution. The Random Forest validation used samples generated through manual interpretation and high-resolution imagery, but no independent field validation was reported. The study did not quantify biomass, carbon loss, CO2-equivalent emissions, uncertainty propagation or spatial spillover beyond camps. No spatial-block validation, SDID, event study, SHAP analysis or counterfactual control landscape was included. Authors also note local residents near some camps were not separated in settlement population analysis; camp-specific fragmentation was not analysed; Bhasan Char relocation and Camp 23 closure may influence dynamics; NDVI did not account for weather/seasonality.</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>P006 provides a detailed and recent camp-level assessment of LULC, fragmentation, NDVI and population distribution, but it remains a two-date descriptive comparison. The proposed research will extend this evidence through an annual 2001–2025 forest-loss and fragmentation panel, treatment and control landscapes beyond official camp boundaries, spatially robust validation, time-varying camp exposure, SDID causal attribution, above-ground carbon-loss estimation, SHAP-based driver interpretation and conservation-priority mapping.</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Very High — Fragmentation and camp-level forest change</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>10.1007/s11111-025-00489-4</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>02_Literature_Review\Research_Papers\02_Fragmentation_Studies\2025_mitra_landscape_fragmentation_population_distribution.pdf</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>DOI or exact title</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Title, metadata and abstract screened</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Open-access full text downloaded and reviewed</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Original Research Article</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Classification method to verify; XAI not identified</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>No/Not identified</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>10.1007/s11111-025-00489-4</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Not downloaded yet</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Litmaps</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>DOI or exact title</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Title, metadata and abstract screened</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Open-access full text available</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Journal Article</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>13 July 2026</t>
@@ -1494,7 +1550,7 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Recent direct comparator for landscape-fragmentation analysis; detailed metrics and temporal design pending full-text extraction</t>
+          <t>Published 27 March 2025; CC BY 4.0. Population analysis: Yes (2024 UNHCR camp-level; settlement change as historical population proxy). Camp 15 forest loss 62.8 vs 62.9 ha inconsistency noted. Extraction notes: P006_2025_mitra_extraction_notes.docx</t>
         </is>
       </c>
     </row>
@@ -1524,57 +1580,67 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Not applicable — methodological study</t>
+          <t>Methodological paper; not geographically specific. Primary empirical illustration: California’s Proposition 99 cigarette-tax intervention, using 39 US states observed from 1970 to 2000. The main worked example uses California as the treated unit, 38 untreated states, 19 pre-treatment periods and 12 post-treatment periods.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Methodological framework: general panel-data setting. Main application: 1970–2000, with California treated from 1989 onward.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Panel-data applications and methodological evaluation; detailed extraction pending</t>
+          <t>Balanced panel data containing N units, T time periods, outcome Y_it, binary treatment indicator W_it, treated and untreated units, and pre-treatment and post-treatment periods. The paper introduces SDID in a balanced-panel setting with repeated unit-level outcomes and binary treatment exposure.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Synthetic Difference-in-Differences estimator</t>
+          <t>Synthetic Difference-in-Differences combines: (1) synthetic-control-style unit weighting; (2) time-period weighting; (3) Difference-in-Differences double differencing; (4) unit fixed effects; (5) time fixed effects; (6) weighted regression estimation. SDID reweights control units to match treated units’ pre-treatment trajectories and reweights pre-treatment periods to resemble post-treatment periods, then estimates the treatment effect through a weighted two-way fixed-effects regression.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Full-text methodological extraction pending</t>
+          <t>The paper introduces Synthetic Difference-in-Differences, which combines synthetic-control unit weighting, time-period weighting and Difference-in-Differences regression. The estimator seeks to improve pre-treatment comparability, remain invariant to additive unit-level differences, and permit large-panel inference. The authors establish conditions for consistency and asymptotic normality under outcome models containing latent unit-by-time factors. The theoretical framework permits interactive latent unit and time factors rather than relying only on simple additive fixed effects.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>No — methodological paper</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Yes — foundational SDID method</t>
+          <t>Yes — foundational Synthetic Difference-in-Differences method</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>The main presentation assumes a balanced panel and binary treatment. Reliable estimation requires treated units to have sufficiently comparable donor units and informative pre-treatment periods. Poor pre-treatment fit or a donor pool lacking common support can produce unstable or concentrated weights. The standard estimator does not automatically resolve interference or spatial spillovers between treated and control locations. Forest outcomes measured in neighbouring grid cells are spatially dependent, requiring spatially appropriate inference beyond the paper’s basic implementations. Time-varying and continuous camp exposure cannot be inserted into the basic binary block-treatment design without additional design decisions. Measurement error in annual forest classification and biomass estimates can propagate into the causal estimates. SDID estimates causal effects only under a defensible treatment, donor pool, timing and no-unmodelled-confounding design; weighting alone does not guarantee causality.</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>P007 provides the causal estimator but does not address environmental remote-sensing outcomes, spatial spillover from refugee camps, fragmentation, biomass uncertainty or time-varying camp expansion. The proposed study will adapt SDID to an annual spatial panel of forest, fragmentation and above-ground carbon outcomes and combine it with remote-sensing validation, spatial sensitivity tests and camp-exposure reconstruction.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Very High — primary causal methodology</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1584,7 +1650,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Not downloaded yet</t>
+          <t>02_Literature_Review\Research_Papers\04_Causal_Inference_Methods\2021_arkhangelsky_synthetic_difference_in_differences.pdf</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1609,7 +1675,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Full text/access status to verify</t>
+          <t>Open full-text revised manuscript downloaded and reviewed; journal metadata verified from the American Economic Association.</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1629,7 +1695,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Foundational methodological reference for the proposed causal-attribution analysis; not a Rohingya-specific empirical study</t>
+          <t>Foundational methodological reference for the proposed causal-attribution analysis; not a Rohingya-specific environmental case study. Open text reviewed from NBER WP 25532 (Revised July 2021).</t>
         </is>
       </c>
     </row>
@@ -1654,37 +1720,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Unpublished working paper</t>
+          <t>Working paper — under review (author-hosted draft, 11 November 2025)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cox's Bazar and areas surrounding Rohingya refugee camps</t>
+          <t>Cox’s Bazar District and adjacent Naikhongchhari subdistrict, Bangladesh. Primary analysis covers areas around Rohingya camp boundaries; Chittagong District is used as an alternative comparison area. The primary dataset includes Cox’s Bazar and Naikhongchhari, while Chittagong is introduced as a robustness donor/comparison area.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2016–2023</t>
+          <t>Land-cover panel: 2016–2023. Pre-treatment observations: February 2016 and February 2017. Treatment/influx: August 2017. Post-treatment observations: February 2018–February 2023. Nighttime lights: 2013–2021. February 2017 is treated as the final pre-treatment observation because it predates the August 2017 mass influx.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Dynamic World 10 m land-cover data; camp boundaries; additional spatial variables</t>
+          <t>Dynamic World 10 m probabilistic LULC data; UNHCR/IOM ISCG camp-boundary polygons; Protected Planet WDPA polygons; VIIRS annual nighttime-light composites; Cox’s Bazar Panel Survey 2019 contextual evidence; administrative-boundary data. Dynamic World provides probabilities for water, trees, shrubs, grasses, built-up, flooded vegetation, crops, bare ground and snow/ice. The study uses probability layers rather than hard classifications. All February Dynamic World layers were averaged separately for each year from 2016 to 2023; upscaled from 10 m to 30 m; initial analytical sample 2,899,227 30 m grid cells.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Propensity-score matching and Difference-in-Differences event study</t>
+          <t>Propensity-score matching (probit; nearest neighbour K=1; caliper 0.1; common support) at 1 km grids using 2016–2017 land-cover probabilities and protected-area share, followed by a matched Difference-in-Differences event study on 30 m cells with grid-cell and year fixed effects and standard errors clustered at 1 km intersections. Treatment: 0–5 km from camp boundaries. Control: &gt;20 km. Spillover zone 5–20 km excluded. Not SDID.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Forest cover declined by 4.6 percentage points by 2019 (~12% below matched baseline), then attenuated to about −2.6 to −3.3 points in 2020–2022 and −1.7 points in 2023. Settlement cover rose by approximately 3.4–3.7 percentage points by 2022–2023 (~44% above baseline). Kutupalong effects were stronger (2019 forest ~−5.8 points; settlement ~+4.6 to +4.8 points). Protected-area peak forest effect ~−3.2 points. Nighttime lights rose ~+0.2 radiance units by 2021 (~4× the 2016 treatment baseline).</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes — annual matched causal event-study estimates</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1699,12 +1765,22 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>No — uses an ML-derived land-cover dataset</t>
+          <t>ML: No independent model trained; Dynamic World machine-learning land-cover product used; XAI: No</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes — propensity-score matching plus DiD event study with unit and year fixed effects</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Only two pre-treatment observations are available, producing only one estimable pre-treatment event-study coefficient. The assumption that the 2016–2017 treatment–control trend represents earlier unobserved trends cannot be tested directly. Camp exposure is defined using fixed distance to mapped camp boundaries rather than annual time-varying camp expansion. Dynamic World probabilities contain classification uncertainty, especially for rural settlement and dry-season agriculture. The 10 m data were upscaled to 30 m, potentially smoothing fine-scale forest and settlement changes. Matching improves observed pre-treatment balance but cannot eliminate unobserved time-varying confounding. Spatial interference may extend beyond the omitted 5–20 km zone and contaminate the wider control pool. The study does not quantify fragmentation, biomass, carbon loss, CO₂-equivalent emissions or land-cover classification uncertainty. LPG cookstove and fencing effects cannot be separately identified. Nighttime-light matching has limited support because rural radiance is very low and several standardized differences remain above 0.1. The study is currently an under-review working paper.</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>P008 already provides annual 2016–2023 land-cover outcomes, propensity-score matching and a Difference-in-Differences event study. Therefore, the proposed research cannot claim novelty merely from using annual data, matching, an event study, or causal land-cover attribution. The proposed contribution must extend this evidence through a much longer 2001–2025 pre-treatment panel, time-varying camp exposure, SDID donor and time weighting, spatial-interference diagnostics, annual fragmentation outcomes, above-ground carbon attribution, classification and biomass uncertainty, SHAP-based predictive-driver interpretation and conservation-priority mapping.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1714,12 +1790,12 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>No DOI verified; author-hosted working paper</t>
+          <t>No DOI verified; https://colettesalemi.ca/files/CB_LC_2025.pdf</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Not downloaded yet</t>
+          <t>02_Literature_Review\Research_Papers\04_Causal_Inference_Methods\2025_salemi_rohingya_camps_land_cover_change.pdf</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1744,7 +1820,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Working-paper full text available</t>
+          <t>Open author-hosted working-paper full text and technical appendix downloaded and reviewed.</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1754,7 +1830,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No — under review</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1764,7 +1840,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>PDF dated 11 November 2025; author's current CV lists it as a 2026 working paper under review</t>
+          <t>Extends the earlier collaboration underlying P002 (World Bank WP 9948). Strongest existing annual causal land-cover event-study benchmark for the Rohingya camp landscape. Constrains novelty claims on annual data, matching and event-study designs.</t>
         </is>
       </c>
     </row>
@@ -1789,109 +1865,119 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GI_Forum 2015, Volume 3 / Journal for Geographic Information Science</t>
+          <t>GI_Forum — Journal for Geographic Information Science (2015); volume numbering inconsistent across publisher page (Vol. 3) and PDF header / institutional record (1-2015 / Vol. 1)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lukole refugee camp, Tanzania</t>
+          <t>Lukole refugee camp and surrounding landscape, Tanzania. The analytical extent used a 16 km buffer around the maximum camp footprint to include both directly affected and comparatively less-affected surrounding landscapes. The buffer was informed by earlier evidence that visible vegetation damage was concentrated within about 2 km, while wood collection could extend 10 km or more from the camp.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Overall satellite archive: December 1990–January 2015. Camp-impact period: 1994–2008. Post-dismantling monitoring: 2008–2015. Change-analysis time steps: six approximately five-year intervals between 1990 and 2015. Camp established 1994; maximum extent ~13 km² in 2000; dismantled 2008; final observation 2015 (~7 years after dismantling).</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>More than 40 Landsat scenes from the USGS EarthExplorer archive. Sensors: Landsat 5, Landsat 7, Landsat 8. Ancillary information: published camp-boundary analysis, refugee activity-radius evidence, camp establishment/dismantling records and restoration information.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Fully automated multi-sensor pre-classification using the Spectral Knowledge-Based Satellite Image Automatic Mapper (SIAM). Primary SIAM outputs: (1) pre-classification containing 33 spectral classes; (2) automatically generated greenness index. Change method: Object-Based Change Detection applied to greenness-index time series to identify vegetation decrease and increase. TOA reflectance preprocessing with automated cloud/shadow support through SIAM.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Deforestation occurred primarily between camp establishment (1994) and dismantling (2008). Vegetation degradation was concentrated around the camp. Detectable reforestation tendencies began around 2000; relatively few changes between 2010 and 2015 suggested most observable reforestation had already occurred before 2010. UNHCR planted ~14 million tree seedlings in northern Tanzania from 1995. Authors describe results as preliminary.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>Yes — long-term vegetation decline associated with the camp lifecycle</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>No — no formal fragmentation metrics</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>No conventional trained ML model; rule-based automated spectral pre-classification: Yes; XAI: No</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>No — descriptive longitudinal remote-sensing analysis</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>The article is a four-page short paper reporting preliminary rather than final results. It does not provide exact areas or rates of total deforestation and reforestation. Only six selected time steps were used in the main change analysis, despite more than 40 scenes being initially processed. Phenological differences, interannual rainfall variability, cloud cover and the use of Landsat 5, 7 and 8 complicated cross-date comparison. The object-based change analysis was based primarily on the greenness index; the complete 33-class pre-classification had not yet been integrated into the final change analysis. No classification-accuracy assessment, confusion matrix, field validation or uncertainty analysis is reported. Some detected changes away from the camp were attributed to agriculture and phenological differences, creating attribution ambiguity. The analysis contains no counterfactual control design, fragmentation metrics, biomass/carbon assessment or formal causal inference.</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>P009 demonstrates the value of monitoring the complete lifecycle of a refugee camp, including the pre-establishment period, operational phase, dismantling and post-camp reforestation. However, it reports preliminary qualitative change patterns rather than validated annual quantitative outcomes. It does not estimate fragmentation, carbon change, causal effects or uncertainty. The proposed research will adapt the long-lifecycle perspective to Cox’s Bazar using annual 2001–2025 outcomes, validated forest-loss and fragmentation metrics, above-ground carbon accounting, SDID counterfactual attribution and explicit post-2019 recovery analysis.</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>High — comparative methodological and restoration reference</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>10.1553/giscience2015s434</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>02_Literature_Review\Research_Papers\05_Comparative_Refugee_Environment_Studies\2015_langer_lukole_refugee_camp_landsat_monitoring.pdf</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Related-paper discovery; first batch screening</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Title and abstract screened</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Open-access full-text short paper downloaded and reviewed.</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Short Paper / Journal Article</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>10.1553/giscience2015s434</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Not downloaded yet</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Litmaps</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Related-paper discovery; first batch screening</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Title and abstract screened</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Journal Article</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>13 July 2026</t>
@@ -1899,7 +1985,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Methodological reference; restoration. Methodological reference; study area is Lukole refugee camp, Tanzania, not Bangladesh.</t>
+          <t>Comparative refugee-environment reference (Lukole, Tanzania). Restoration monitoring: Yes. Volume numbering inconsistent (publisher Vol. 3 vs PDF 1-2015). Preliminary qualitative findings only; no quantitative area estimates.</t>
         </is>
       </c>
     </row>
@@ -1915,7 +2001,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1924,32 +2010,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Land Degradation &amp; Development</t>
+          <t>Land Degradation &amp; Development, 32(13), 3666–3683</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cox's Bazar–Teknaf Peninsula, Bangladesh</t>
+          <t>Cox’s Bazar–Teknaf Peninsula, focusing on 23 forest beats within the Cox’s Bazar South Forest Division and an additional portion of Naikhongchhari beat in Bandarban Forest Division. The study used Bangladesh Forest Department administrative units because most refugee camps were established within the South Forest Division. Study-area extent ~41,162 ha.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Observed LULC comparison: 2017–2019. Exact Sentinel-2A dates: 18 February 2017, 18 February 2018 and 13 February 2019. Prediction years: 2023 and 2027.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Multi-temporal Sentinel-2A imagery (10 m; SEN2COR surface reflectance); Bangladesh Forest Department forest-beat boundaries; UNHCR camp polygons; RapidEye, WorldView-2, Google Earth and UAV reference imagery; SRTM DEM; population, physiography, accessibility and other dynamic driver variables; IOM &amp; FAO (2017) aboveground biomass inventory (57 subplots).</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Hybrid ISODATA + Maximum Likelihood supervised multi-date LULC classification; post-classification forest-change analysis; multi-criteria evaluation of degradation drivers; Cellular Automata–Markov modelling for 2023 and 2027; above-ground biomass and carbon-stock estimation (carbon = AGB/2) to represent loss of ecosystem function.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Between 2017 and 2019, approximately 3,130 ha of forest-cover categories were transformed into refugee camps or Rohingya-influenced degraded forest. Under a business-as-usual scenario, degraded forest was projected to increase by ~3,080 ha by 2023 and ~5,115–5,120 ha by 2027 relative to 2019. Carbon release was estimated at ~27,600 tons (2017–2019) and ~71,920 tons (2017–2027 projection); total carbon stock fell from 221,841 t (2017) to 194,238 t (2019).</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1959,22 +2045,32 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Discussed as ecological consequence, but no formal landscape fragmentation metrics verified</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>Yes — above-ground biomass and carbon-stock loss estimated</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>No modern predictive ML/XAI framework; supervised classification and CA–Markov modelling used</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No — descriptive change analysis and scenario prediction</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>The observed forest-change analysis covers only 2017–2019, providing a very short empirical period. The CA–Markov predictions assume continuation of historical transition probabilities and selected driving factors; they are scenario projections rather than causal forecasts. Future refugee population, policy interventions, LPG adoption, fencing, restoration, camp consolidation and economic change may invalidate the business-as-usual transition structure. Cloud-free imagery availability constrained seasonal analysis. The study relied on optical imagery and could not assess monsoon-season conditions; the authors recommend radar data for future work. Biomass and carbon estimates are model-derived rather than validated with extensive camp-area field plots. No counterfactual donor/control landscape was used. No SDID, event study, spatial-interference analysis or causal attribution was performed. No formal patch, connectivity, core-area or edge-fragmentation metrics were calculated. Classification, transition-model and biomass uncertainties were not propagated jointly into the final carbon-loss estimates. The model does not use SHAP or another explainable-driver framework.</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>P010 integrates forest degradation, CA–Markov prediction, above-ground biomass and carbon-stock loss, making it one of the closest existing studies to the proposed integrated framework. However, it is based on a short 2017–2019 observed period and business-as-usual scenario projection rather than a long annual historical panel or causal counterfactual. The proposed research will extend this work through annual 2001–2025 forest outcomes, formal fragmentation metrics, spatially explicit ESA CCI/GEDI-supported above-ground carbon accounting, SDID causal attribution, time-varying camp exposure, measurement-uncertainty propagation and SHAP-based driver analysis.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1989,7 +2085,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Not downloaded yet</t>
+          <t>02_Literature_Review\Research_Papers\01_Direct_Rohingya_Forest_Studies\2021_hasan_forest_degradation_ecosystem_function.pdf</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -2014,12 +2110,12 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>Author-uploaded full text reviewed from ResearchGate public full text and Authorea GREEN OA preprint; automated binary PDF download blocked by Cloudflare — archival working PDF saved (replace with ResearchGate/Authorea PDF when available).</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Research Article / Special Issue Article</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -2034,7 +2130,7 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Direct forest change. Core empirical study; publication metadata should be verified during full-text collection.</t>
+          <t>Online first: 2020 (accepted 3 Nov 2020; online 6 Nov 2020). Final issue citation year: 2021. Predicted 2027 loss reported as ~5,115 ha (abstract), 5,119.02 ha (Table 5) and ~5,120 ha (discussion). Shrubs/plantation AGB densities of 2 kg/ha in manuscript appear anomalous.</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2142,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sarkar, S. K.; Saroar, M. M.; Chakraborty, T.</t>
+          <t>Sarkar, S. K.; Saroar, M.; Chakraborty, T.</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2054,7 +2150,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Navigating Nature's Toll: Assessing the Ecological Impact of the Refugee Crisis in Cox's Bazar, Bangladesh</t>
+          <t>Navigating nature’s toll: Assessing the ecological impact of the refugee crisis in Cox’s Bazar, Bangladesh</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2064,104 +2160,114 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cox's Bazar, Bangladesh</t>
+          <t>Ukhiya and Teknaf Upazilas, Cox’s Bazar District, Bangladesh, covering approximately 57,307.25 ha. The study focuses on the two upazilas containing most Rohingya camps.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Pre/post LULC comparison: 25 August 2017 and 20 March 2021; LST comparison 2017 and 2021. Critical note: 25 August 2017 is labelled pre-influx but coincides with the beginning of the major 2017 displacement.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Sentinel-2A and Sentinel-2B multispectral imagery (10 m visible/NIR); Landsat 8 OLI/TIR (path/row 139/43) for LST; WorldView-2 (0.5 m) and field observations/surveys for 600 reference samples; Bangladesh and Rohingya population data; ecosystem-service value coefficients; land-use-specific carbon emission/absorption coefficients.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Sentinel-based supervised LULC classification using ANN, Random Forest and RBF-SVM; ANN-selected post-classification change analysis; Landsat-derived LST; benefit-transfer ecosystem-service valuation; fuzzy-logic ecological-quality modelling; Markovian EQ-transition analysis.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Forest area decreased by 5,488.01 ha between 2017 and 2021, falling from 24,982.31 ha to 19,494.30 ha. Settlement increased by 4,725.45 ha, from 15,614.00 ha to 20,339.45 ha. ANN produced the highest LULC-classification accuracy, with overall accuracy of 97% in 2017 and 91% in 2021.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>Yes — 5,488.01 ha decline quantified</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>No — discussed ecologically, but no formal fragmentation metrics</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Partial/Indirect — land-use-specific carbon emissions and absorption used as an EQ indicator; no field or biomass-based forest carbon-stock accounting</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>ML: Yes — ANN, RF and SVM; XAI: No</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>No — two-date observational pre/post comparison without a counterfactual control group</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Only two image dates (no annual trajectory/pre-trend/recovery). 2017 baseline (25 Aug) coincides with major-influx onset and is seasonally mismatched with March 2021. Descriptive pre/post design without counterfactual. Benefit-transfer ESV not locally calibrated; settlement ESV=0; aggregate ESV masks forest–water trade-offs. CS ±50% does not propagate classification uncertainty. Fuzzy memberships/GAMMA judgement-based. No formal fragmentation, field AGB/carbon, SDID, SHAP or joint uncertainty. Cloud-free optical constraint; authors recommend radar. Data on request only. Abstract vs Table 5 raw-material/biodiversity % conflict; water narrative conflicts with Table 3.</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>P011 integrates machine-learning land-cover classification, ecosystem-service valuation, land-use carbon indicators, LST and fuzzy ecological-quality assessment. However, it relies on two temporally and seasonally mismatched observations and does not provide a long annual baseline, counterfactual causal attribution, formal fragmentation metrics, field- or satellite-biomass-based carbon accounting, explainable driver analysis or propagated measurement uncertainty. The proposed research will extend this integrated ecological perspective through annual 2001–2025 outcomes, SDID attribution, annual fragmentation, spatial above-ground biomass/carbon loss, spatial-block validation, uncertainty propagation and separate SHAP-based predictive analysis.</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>10.1016/j.heliyon.2023.e18255</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>02_Literature_Review\Research_Papers\01_Direct_Rohingya_Forest_Studies\2023_sarkar_ecological_impact_refugee_crisis.pdf</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Related-paper discovery; first batch screening</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Title and abstract screened</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Full-text reviewed — open-access PMC/publisher PDF (PMC10368913; CC BY 4.0)</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Research Article</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>10.1016/j.heliyon.2023.e18255</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Not downloaded yet</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Litmaps</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Related-paper discovery; first batch screening</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Title and abstract screened</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Journal Article</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>13 July 2026</t>
@@ -2169,7 +2275,7 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Direct ecological/forest impact. Core empirical evidence for ecological impact and ecosystem-service-value change.</t>
+          <t>Open Access CC BY 4.0; online 13 July 2023; Heliyon 9(7):e18255. ESV/EQ treated as supplementary (Decision 014). Also record: Ecological Quality = Yes (fuzzy + Markov).</t>
         </is>
       </c>
     </row>
@@ -2181,11 +2287,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sarkar, S. K.; Saroar, M.; Chakraborty, T.</t>
+          <t>Sarkar, S. K.; Saroar, M. M.; Chakraborty, T.</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2199,104 +2305,114 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ukhiya and Teknaf, Cox's Bazar, Bangladesh</t>
+          <t>Ukhiya and Teknaf upazilas, Cox’s Bazar District, Bangladesh (573.07 km²).</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>LULC/ESV comparison 2017–2021. Exact Sentinel dates: January 2017 (Sentinel-2A, pre-influx) and January 2021 (Sentinel-2B, post-influx). Online first 27 June 2022; final volume year 2023.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Sentinel-2A/2B multispectral imagery (10 m visible/NIR); WorldView-2 (0.5 m) and field observations (800 samples; 640 train / 160 test); UNHCR camp/population information; benefit-transfer ESV coefficients (LULC proxies: cropland/forest/urban/wetland).</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Artificial Neural Network supervised LULC classification; post-classification land-cover change analysis; benefit-transfer ecosystem-service valuation; ecosystem-service category comparison between 2017 and 2021; ±50% coefficient sensitivity (CS).</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Forest lost 54.88 km² (−9.58 pp); settlement increased ~47.25–47.26 km² (+8.25 pp). Total ESV rose from US$310.13 million to US$332.94 million (+US$22.81 million), while raw-material and biodiversity ESV declined by 13.58% and 14.57%. Forest ESV fell US$17.22 million (−21.97%). ANN OA/Kappa: 0.97/0.96 (2017), 0.91/0.89 (2021).</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>Yes — 54.88 km² forest decline reported</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No direct biomass or forest-carbon accounting</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>ML: Yes — ANN land-cover classification; XAI: No</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>No — two-date observational comparison without counterfactual control</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Only two dates; descriptive pre/post without counterfactual. Benefit-transfer coefficients not field-calibrated; settlement/urban coefficients drive aggregate ESV upward and can mask forest-service losses. Classification uncertainty not propagated. No fragmentation, AGB/carbon, SDID or SHAP. Material ESV differences vs P011 require reconciliation; papers are overlapping/non-independent.</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>P012 provides a monetary ecosystem-service interpretation of 2017–2021 LULC change, but it does not provide a long annual baseline, counterfactual causal design, fragmentation analysis, spatial biomass/carbon accounting or propagated uncertainty. The proposed study will treat ESV as supplementary evidence and prioritize physically measurable outcomes: annual forest loss, fragmentation and above-ground carbon loss.</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>High — ecosystem-service valuation evidence</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>10.1017/dmp.2022.125</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>02_Literature_Review\Research_Papers\06_Ecosystem_Service_Studies\2023_sarkar_cost_ecosystem_service_value.pdf</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Related-paper discovery; first batch screening</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Title and abstract screened</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Author/full text reviewed from ResearchGate public full text (pub. 361562126); automated binary PDF download blocked — working archive saved; replace with official author PDF when available.</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Original Research Article</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>ANN classification used; XAI not identified</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>10.1017/dmp.2022.125</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Not downloaded yet</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Litmaps</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Related-paper discovery; first batch screening</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Title and abstract screened</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Journal Article</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>13 July 2026</t>
@@ -2304,7 +2420,7 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Direct forest change; ecosystem services. Litmaps may show 2022; version-of-record appears in the 2023 journal volume. Verify final citation during full-text extraction.</t>
+          <t>Author-year label: Sarkar et al., 2023a (P011 = 2023b). Online first: 27 June 2022. Final volume: 17 (2023) e198. Ecosystem Services: Yes — primary outcome. Decision 015: treat with P011 as related evidence family; do not average ESV.</t>
         </is>
       </c>
     </row>
@@ -2324,114 +2440,124 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>The Rohingya Refugee Crisis in Bangladesh: Assessing the Impact on Land Use Patterns and Land Surface Temperature Using Machine Learning</t>
+          <t>The Rohingya refugee crisis in Bangladesh: assessing the impact on land use patterns and land surface temperature using machine learning</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Environmental Monitoring &amp; Assessment</t>
+          <t>Environmental Monitoring and Assessment</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rohingya camp areas, Cox's Bazar, Bangladesh</t>
+          <t>Historical descriptive analysis: ~24 km² Rohingya camp landscape within Ukhiya and Teknaf, Cox’s Bazar. Prediction domain: wider Ukhiya and Teknaf upazilas. Approx. coordinates 20°54′00″–21°14′00″ N; 92°08′00″–92°16′00″ E.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Historical LULC/LST 1997–2022 (~5-year intervals). Exact Landsat dates: 19 Jan 1997; 09 Jan 2002; 15 Jan 2007; 21 Jan 2012; 26 Jan 2017; 13 Jan 2018; 19 Jan 2020; 08 Jan 2022. CA–ANN calibration 2018+2020→2022; predictions 2028 and 2034.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>30 m Landsat TM/ETM+/OLI-TIRS (cloud &lt;10%, January); 30 m DEM; road and river/stream networks; Google Earth Pro reference imagery; NDVI/NDBI/NDWI for LST prediction drivers.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Multi-date 30 m Landsat LULC and LST analysis using iso-cluster unsupervised classification; TOA radiance, brightness temperature, NDVI-derived emissivity and LST calculation; CA–ANN prediction implemented through MOLUSCE using DEM, roads, streams and post-2017 LULC inputs.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Camp-core settlement rose from 5.28% (1997) and 11.91% (2017) to 70.09% (2022); vegetation fell from 70.26% to 9.73%. Mean January LST rose from 18.86°C (1997) to 21.31°C (2017) and 25.94°C (2022). 2022 LULC validation OA ~92%, Kappa 0.89. Upazila CA–ANN scenarios: settlement 11.63% and vegetation 54.42% by 2034 (~14 km² vegetation loss); area &gt;24°C rises from ~13% (2022) to ~21% (2034).</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>Partial — vegetation decline is quantified, but vegetation combines forest, agriculture, grassland and other cover</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>ML: Yes — CA–ANN used for future LULC/LST simulation; historical classification: iso-cluster unsupervised; XAI: No</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>No — descriptive historical analysis and scenario prediction</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Five-year intervals; incomplete Landsat cross-sensor harmonization; broad vegetation class; OA only for 2022 (60 GE points); NDVI–LST R² mislabelled as correlation; camp-core vs upazila domains not comparable; CA–ANN continuation assumption without policy/LPG/restoration; no SDID/fragmentation/carbon/uncertainty/SHAP; hyperparameters incompletely reported. Landsat 8–9 label for pre-LS9 dates.</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>P013 provides a long multi-date perspective on settlement, vegetation and LST change and demonstrates CA–ANN scenario prediction, but lacks annual forest-specific outcomes, formal fragmentation, above-ground carbon, counterfactual SDID attribution, time-varying camp exposure, spatial-block validation, SHAP and uncertainty propagation. Proposed work will separate annual measurement, SDID attribution, validated prediction and SHAP interpretation with consistent spatial units.</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>10.1007/s10661-024-12701-3</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>02_Literature_Review\Research_Papers\01_Direct_Rohingya_Forest_Studies\2024_ahmed_rohingya_lulc_lst_machine_learning.pdf</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Related-paper discovery; first batch screening</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Title and abstract screened</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Full-text reviewed. Full article text reviewed from the author-uploaded public version; binary author PDF to be archived when available.</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Research Article</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>10.1007/s10661-024-12701-3</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Not downloaded yet</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Litmaps</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Related-paper discovery; first batch screening</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Title and abstract screened</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Journal Article</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>13 July 2026</t>
@@ -2439,7 +2565,7 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Machine learning; forest/LULC. Important comparator for the proposed predictive ML component; SHAP and spatial validation must be checked from full text.</t>
+          <t>Vol. 196 Issue 6 article 555; published 18 May 2024. LST: Yes. Prediction: Yes (2028/2034). Dual spatial domains (camp-core vs upazila). Decision 016 applies. RG pub. 380694917.</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2577,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gromny, E.; Jenerowicz-Sanikowska, M.; Haarpaintner, J.; et al. (13 authors)</t>
+          <t>Gromny, E.; Jenerowicz-Sanikowska, M.; Haarpaintner, J.; Aleksandrowicz, S.; Woźniak, E.; Pesquer Mayos, L.; Chułek, M.; Sobczak-Szelc, K.; Wawrzaszek, A.; Sala, S.; Espegren, A.; Starczewski, D.; Pawlak, Z.</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2459,7 +2585,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Remote Sensing Insights into Land Cover Dynamics and Socio-Economic Drivers: The Case of Mtendeli Refugee Camp, Tanzania (2016–2022)</t>
+          <t>Remote sensing insights into land cover dynamics and socio-economic Drivers: The case of Mtendeli refugee camp, Tanzania (2016–2022)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2469,104 +2595,114 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mtendeli refugee camp, Tanzania</t>
+          <t>Mtendeli Refugee Camp and surrounding landscape, Kigoma Region, north-western Tanzania. Remote-sensing AOI: 40 × 40 km. Zones: camp (~2 km radius); 0–5 km; 5–10 km; 10–15 km buffers.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Annual land-cover maps 2016–2022. Camp operation 2016–2021 (opened 2016; peak 2017; closed December 2021); post-closure 2022. Field validation July 2022.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Sentinel-1 SAR (VV/VH, quarterly mosaics); Sentinel-2 multi-date optical (~10–15 scenes/year, Sen2Cor); Landsat-8 SR for 2016 supplementation; SRTM DEM; ESA WorldCover 2020; OpenStreetMap built-up; RapidEye context; UNHCR factsheets; agricultural statistics; July 2022 field observations; semi-structured key-informant interviews; NGO/institutional reports.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Annual 10 m pixel-based Random Forest land-cover classification using multi-date Sentinel-2 optical imagery, quarterly Sentinel-1 VV/VH mosaics, all normalized spectral-band combinations, WorldCover-derived and locally refined training data, probability aggregation, post-classification transition analysis, distance buffers, field validation and qualitative driver triangulation.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Full-text extraction pending</t>
+          <t>Artificial surfaces rose by &gt;26 percentage points in 2017; &gt;20% of camp/nearest surroundings transformed during 2016–2021. Tree-cover conversion affected ~6% of the AOI; change intensity declined with distance (strongest within ~2 km; influence to ~10 km). Cropland expanded after 2018 via shrub/grassland/tree conversions linked to refugee and host-community drivers. After 2021 closure, cropland fell and managed woody vegetation/natural succession increased (~80% of former camp in veg classes by 2022). OA 83.46% (2020); 82% (July 2022 single image).</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>Yes — annual tree-cover and natural-vegetation transitions analysed</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>No — no formal patch, edge, core or connectivity metrics</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>ML: Yes — Random Forest annual classification; XAI: No</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>No — annual descriptive change and driver interpretation, without counterfactual controls</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Starts in 2016 after construction began; only seven years; independent accuracy only for 2020 annual map and July 2022 single image; WorldCover-2020 training transferred across years; 2022 managed-woody legend change; vegetation-class confusion; 10 m cannot map small camp features; Landsat-8 only in 2016; distance buffers approximate exposure; interviews not causal; no SDID/fragmentation/carbon/uncertainty propagation.</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>P014 already demonstrates annual multi-sensor mapping, distance-gradient analysis, field validation, interviews, lifecycle monitoring and post-closure restoration. Proposed Cox’s Bazar work cannot claim novelty from those elements alone and must extend via longer 2001–2025 panel, clean pre-treatment, time-varying exposure, SDID, spillover diagnostics, fragmentation, attributable carbon, uncertainty propagation, SHAP prediction and conservation-priority mapping.</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>High — comparative annual, distance-gradient and recovery method</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>10.1016/j.rsase.2024.101334</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>02_Literature_Review\Research_Papers\05_Comparative_Refugee_Environment_Studies\2024_gromny_mtendeli_land_cover_drivers.pdf</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Litmaps</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Related-paper discovery; first batch screening</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Title and abstract screened</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Full-text reviewed — open access (CC BY-NC 4.0); author-uploaded public full text reviewed (RG 383935650); binary PDF to be archived when available.</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Research Article</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>10.1016/j.rsase.2024.101334</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Not downloaded yet</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Litmaps</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Related-paper discovery; first batch screening</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Title and abstract screened</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Journal Article</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>13 July 2026</t>
@@ -2574,7 +2710,7 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Transferable remote-sensing methodology. Methodological comparator from Mtendeli camp, Tanzania; not direct evidence for Cox's Bazar.</t>
+          <t>Available online 10 September 2024; Vol. 36 article 101334. Restoration: Yes. Qualitative methods: Yes. Comparative Tanzania case — not Cox’s Bazar evidence. Decision 017 applies.</t>
         </is>
       </c>
     </row>
@@ -3255,6 +3391,1943 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="85" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Extracted Value</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Source/Section</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Paper ID</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>10.1553/giscience2015s434</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PDF header</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Pages</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>4 (short paper)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Volume note</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Publisher Vol. 3 vs PDF 1-2015 / Vol. 1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Metadata inconsistency</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Camp lifecycle</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Established 1994; max ~13 km² / 130k+ (2000); dismantled 2008</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Buffer</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>16 km around maximum camp footprint</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>&gt;40 cloud-free Landsat scenes; Dec 1990–Jan 2015</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Landsat 5, 7, 8</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Methods/Discussion</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Change time steps</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>6 at ~5-year intervals</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Preprocessing</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>TOA reflectance; SIAM cloud/shadow masks</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Change method</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>OBCD on SIAM greenness index</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Methods/Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Deforestation</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Mainly 1994–2008 around camp</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Preliminary Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Reforestation</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Tendencies from ~2000; little change 2010–2015</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Preliminary Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Restoration</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>UNHCR ~14 million seedlings from 1995</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Introduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>None reported</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Our appraisal</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Causal inference</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Restoration relevance</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Post-camp recovery monitoring</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Discussion</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Research gap</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Need quantitative annual outcomes, fragmentation, carbon, SDID</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Our appraisal</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="85" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Extracted Value</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Paper ID</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Year (matrix)</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Final issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Online first</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>6 November 2020</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Wiley history</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Received / Accepted</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>26 Jun 2020 / 3 Nov 2020</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Article header</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>10.1002/ldr.3821</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Wiley</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sentinel-2A dates</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>2017-02-18; 2018-02-18; 2019-02-13</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Study area</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>~41,162 ha; 23 South Division beats + Naikhongchhari portion</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LULC classes</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>14 classes including SH, MF, PT, CF, CA, DF</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Classifier</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>ISODATA signatures + Maximum Likelihood + post-refinement</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Accuracy points</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>100 stratified points per class</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OA / Kappa 2017–19</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>86.85/0.86; 89.12/0.88; 91.45/0.91</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Observed conversion</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>~3,130 ha forest categories to camps/degraded forest (2017–2019)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CA–Markov validation</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>2019 OA 86.21%; kappa 0.85</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Predicted DF 2019–2023</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>+3,080.1 ha</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Table 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Predicted DF 2019–2027</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>+5,119.02 ha (~5,115–5,120)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Table 5/Abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Carbon 2017 / 2019 / 2027</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>221,841 / 194,238 / 149,919 tons</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Table 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Carbon release</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>~27,600 t (2017–19); ~71,920 t (2017–27 proj.)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AGB source</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>IOM &amp; FAO 2017; 57 subplots; carbon = AGB/2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Causal method</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>None — descriptive + scenario prediction</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Extracted Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Paper ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10.1016/j.heliyon.2023.e18255</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Journal</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Heliyon 9(7): e18255</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13 July 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Access</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Open Access — CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PMC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PMC10368913</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Study area</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ukhiya &amp; Teknaf; 57,307.25 ha</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sentinel dates</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2017-08-25; 2021-03-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Landsat path/row</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>139/43 (LST 2017 &amp; 2021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Reference samples</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>600 (WV-2 + field); train 480 / test 120</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LULC classes</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Agriculture; Forest; Settlement; Water</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ANN settings</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1,000 iterations</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RF settings</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ntree=500; mtry=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SVM settings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>RBF kernel; C tuned</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ANN OA/Kappa</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2017: 0.97 / 0.96; 2021: 0.91 / 0.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>RF OA/Kappa</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2017: 0.95 / 0.94; 2021: 0.90 / 0.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SVM OA/Kappa</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2017: 0.89 / 0.86; 2021: 0.86 / 0.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Forest change</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>24,982.31 → 19,494.30 ha (−5,488.01 ha; −9.58 pp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Settlement change</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>15,614 → 20,339.45 ha (+4,725.45 ha; +8.25 pp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total ESV</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>US$67.83m (2017) → US$67.78m (2021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Forest ESV</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>US$24.26m → US$18.93m (−US$5.33m; −21.97%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Water ESV</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>+US$5.27m (+12.41%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EQ model</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>7 params; fuzzy small/large; GAMMA 0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>EQ transitions</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>VG→bad/VB 24.2%; Mod→good 61%; Bad→mod 73%; VB→bad 74%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>VG area lost</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>133.67 km² very-good EQ transitioned away</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Carbon role</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Land-use emission/absorption EQ indicator only</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Fragmentation</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Discussed; no formal metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Causal design</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Two-date observational; no counterfactual</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Inconsistency: abstract vs Table 5</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raw material 13.58% vs 21.97%; biodiversity 14.57% vs 2.29% — use Table 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Inconsistency: water narrative</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Text says decreased; Table 3 shows +620.48 ha</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Baseline timing</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>25 Aug 2017 labelled pre-influx but coincides with mass influx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Extraction notes</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>P011_2023_sarkar_extraction_notes.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>02_Literature_Review\Research_Papers\01_Direct_Rohingya_Forest_Studies\2023_sarkar_ecological_impact_refugee_crisis.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Extracted Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Paper ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>APA label</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sarkar et al. (2023a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Year (matrix)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Online first</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>27 June 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Journal</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Disaster Medicine and Public Health Preparedness 17:e198</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>10.1017/dmp.2022.125</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Image dates</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>January 2017 (S2A); January 2021 (S2B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Samples</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>800 (640 train / 160 test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ANN OA/Kappa</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2017: 0.97/0.96; 2021: 0.91/0.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Forest change</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>−54.88 km² (−9.58 pp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Settlement change</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>+47.25 km² Table 2 / 47.26 km² abstract (+8.25 pp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total ESV</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>US$310.13m → US$332.94m (+22.81m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Forest ESV</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>−US$17.22m (−21.97%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Raw materials</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>−13.58%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Biodiversity</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>−14.57%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Settlement coeff role</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>≈6661 vs forest ≈3135; drives aggregate ESV up</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>vs P011 ESV</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Materially different totals; do not merge/average</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Extraction notes</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>P012_2023_sarkar_extraction_notes.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>02_Literature_Review\Research_Papers\06_Ecosystem_Service_Studies\2023_sarkar_cost_ecosystem_service_value.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Extracted Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Paper ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10.1007/s10661-024-12701-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Journal</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Environ Monit Assess 196(6):555</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>18 May 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Historical AOI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>~24 km² camp landscape</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Prediction AOI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ukhiya + Teknaf upazilas</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Landsat dates</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1997-01-19; 2002-01-09; 2007-01-15; 2012-01-21; 2017-01-26; 2018-01-13; 2020-01-19; 2022-01-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Iso-cluster unsupervised; 4 classes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Vegetation definition</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sparse/thick veg, trees, grassland, agriculture</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2022 OA/Kappa</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>~92% / 0.89 (60 GE points)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Camp settlement %</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5.28 → 11.91 → 70.09 (1997/2017/2022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Camp vegetation %</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>70.26 → 52.88 → 9.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Mean Jan LST °C</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>18.86 → 21.31 → 25.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CA–ANN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MOLUSCE QGIS 2.18.26; 2018+2020→2022; iter3=2028; iter6=2034</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Upazila settlement %</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5.77 (2018); 4.97 (2022); 7.98 (2028); 11.63 (2034)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Upazila vegetation %</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>56.80 (2022) → 54.42 (2034); ~14 km² loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LST &gt;24°C area</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>~13% → 17% → 21% (2022/2028/2034)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NDVI–LST 0.8825</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Appears to be R²; mislabelled as correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sensor-label flag</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Table 1 Landsat 8–9 for 2017–2020 dates</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Extraction notes</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>P013_2024_ahmed_extraction_notes.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>02_Literature_Review\Research_Papers\01_Direct_Rohingya_Forest_Studies\2024_ahmed_rohingya_lulc_lst_machine_learning.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Extracted Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Paper ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P014</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10.1016/j.rsase.2024.101334</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Access</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Open Access — CC BY-NC 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>10 September 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Camp</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mtendeli, Kigoma, Tanzania</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AOI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>40 × 40 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Buffers</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Camp ~2 km; 0–5; 5–10; 10–15 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Lifecycle</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2016 open; 2017 peak; Dec 2021 close; 2022 post</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Classifier</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Random Forest + annual probability aggregation</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OA 2020 / 2022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>83.46% / 82.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Validation n</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2092 (2020); July 2022 field points</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Artificial surfaces 2017</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>&gt;26 percentage-point increase</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Near-camp transform 2016–21</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>&gt;20% of camp+closest zone</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tree-cover conversion AOI</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>~6% (2016–2021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fuelwood distances</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>~4 km permitted; later ~10–12 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2022 camp veg classes</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>~80% (incl. managed woody)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Post-closure natural veg</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>~50% camp; ~15% nearest zone</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Extraction notes</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>P014_2024_gromny_extraction_notes.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>02_Literature_Review\Research_Papers\05_Comparative_Refugee_Environment_Studies\2024_gromny_mtendeli_land_cover_drivers.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -3272,8 +5345,8 @@
     <col width="37.7109375" customWidth="1" style="2" min="4" max="4"/>
     <col width="18" customWidth="1" style="2" min="5" max="7"/>
     <col width="44" customWidth="1" style="2" min="8" max="8"/>
-    <col width="9.140625" customWidth="1" style="2" min="9" max="9"/>
-    <col width="9.140625" customWidth="1" style="2" min="10" max="16384"/>
+    <col width="9.140625" customWidth="1" style="2" min="9" max="10"/>
+    <col width="9.140625" customWidth="1" style="2" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3692,7 +5765,8 @@
   <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="19"/>
+    <col width="18" customWidth="1" style="10" min="1" max="19"/>
+    <col width="9.140625" customWidth="1" style="10" min="20" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3792,991 +5866,991 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="210" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>C001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Langer, 2015</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Long-term Monitoring of the Environmental Impact of a Refugee Camp Based on Landsat Time Series: The Example of Deforestation and Reforestation During the Whole Lifespan of the Camp Lukole, Tanzania</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>Langer, S.; Tiede, D.; Lüthje, F.</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="10" t="n">
         <v>2015</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>GI_Forum 2015, Volume 3 / Journal for Geographic Information Science</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>10.1553/giscience2015s434</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>Hassan 2023 clearly visible; additional connections to verify</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="10" t="inlineStr">
         <is>
           <t>Conservation and Restoration</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="10" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>Provides a transferable long-term Landsat time-series framework for assessing deforestation and reforestation across the complete lifecycle of a refugee camp.</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="10" t="inlineStr">
         <is>
           <t>P009</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="10" t="inlineStr">
         <is>
           <t>13 July 2026</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" s="10" t="inlineStr">
         <is>
           <t>Methodological reference; study area is Lukole refugee camp, Tanzania, not Bangladesh.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="165" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>C002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Hasan, 2020</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Spatiotemporal Pattern of Forest Degradation and Loss of Ecosystem Function Associated with Rohingya Influx: A Geospatial Approach</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Hasan, M. E.; Zhang, L.; Dewan, A.; Guo, H.; Mahmood, R.</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="10" t="n">
         <v>2020</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Land Degradation &amp; Development</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>10.1002/ldr.3821</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>Multiple seed connections — exact connection unclear</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>Direct Forest Change</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>Directly examines spatiotemporal forest degradation and loss of ecosystem function associated with the Rohingya influx using geospatial analysis.</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="10" t="inlineStr">
         <is>
           <t>P010</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R3" s="10" t="inlineStr">
         <is>
           <t>13 July 2026</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" s="10" t="inlineStr">
         <is>
           <t>Core empirical study; publication metadata should be verified during full-text collection.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="120" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>C003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Sarkar, 2023</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Navigating Nature's Toll: Assessing the Ecological Impact of the Refugee Crisis in Cox's Bazar, Bangladesh</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Sarkar, S. K.; Saroar, M. M.; Chakraborty, T.</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="10" t="n">
         <v>2023</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Heliyon</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>10.1016/j.heliyon.2023.e18255</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Multiple seed connections — exact connection unclear</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>To verify</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>Direct Forest Change</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="10" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>Directly assesses forest, settlement and ecological-service changes associated with the Rohingya refugee crisis in Cox's Bazar.</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" s="10" t="inlineStr">
         <is>
           <t>P011</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R4" s="10" t="inlineStr">
         <is>
           <t>13 July 2026</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>Core empirical evidence for ecological impact and ecosystem-service-value change.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="135" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>C004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Sarkar, 2022</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Cost of Ecosystem Service Value Due to Rohingya Refugee Influx in Bangladesh</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Sarkar, S. K.; Saroar, M.; Chakraborty, T.</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="10" t="n">
         <v>2022</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Disaster Medicine and Public Health Preparedness</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>10.1017/dmp.2022.125</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>Multiple seed connections — exact connection unclear</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>Direct Forest Change</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>Estimates land-cover change and the economic cost of ecosystem-service loss associated with the Rohingya influx in Ukhiya and Teknaf.</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" s="10" t="inlineStr">
         <is>
           <t>P012</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R5" s="10" t="inlineStr">
         <is>
           <t>13 July 2026</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>Litmaps may show 2022; version-of-record appears in the 2023 journal volume. Verify final citation during full-text extraction.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>C005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Ahmed, 2024</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>The Rohingya Refugee Crisis in Bangladesh: Assessing the Impact on Land Use Patterns and Land Surface Temperature Using Machine Learning</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Ahmed, F.; Alam, S.; Saha, O. R.; Rahman, A.</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="10" t="n">
         <v>2024</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Environmental Monitoring &amp; Assessment</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>10.1007/s10661-024-12701-3</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>Multiple seed connections — exact connection unclear</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="10" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="10" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>Direct Rohingya-camp study combining machine learning, land-use analysis and land-surface-temperature assessment.</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" s="10" t="inlineStr">
         <is>
           <t>P013</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R6" s="10" t="inlineStr">
         <is>
           <t>13 July 2026</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>Important comparator for the proposed predictive ML component; SHAP and spatial validation must be checked from full text.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>C006</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Gromny, 2024</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Remote Sensing Insights into Land Cover Dynamics and Socio-Economic Drivers: The Case of Mtendeli Refugee Camp, Tanzania (2016–2022)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Gromny, E.; Jenerowicz-Sanikowska, M.; Haarpaintner, J.; et al. (13 authors)</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="10" t="n">
         <v>2024</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>Remote Sensing Applications: Society and Environment</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>10.1016/j.rsase.2024.101334</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>Multiple seed connections — exact connection unclear</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>To verify</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>Direct Forest Change</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>Provides a recent transferable remote-sensing design for analysing land-cover dynamics and socioeconomic drivers around a refugee camp.</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" s="10" t="inlineStr">
         <is>
           <t>P014</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R7" s="10" t="inlineStr">
         <is>
           <t>13 July 2026</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>Methodological comparator from Mtendeli camp, Tanzania; not direct evidence for Cox's Bazar.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="135" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>C007</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Mohiuddin, 2025</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Assessing the Impact of Land Use Land Cover Change after Rohingya Forced Migration on Elephant Route in Cox's Bazar District, Bangladesh</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Mohiuddin, M.; Hossain, M.; Islam, M. Y.; Nowreen, S.; Sultana, N.</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="10" t="n">
         <v>2025</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Landscape and Ecological Engineering</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>10.1007/s11355-025-00642-z</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>Multiple seed connections — exact connection unclear</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>To verify</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>Conservation and Restoration</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="10" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="10" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>Directly evaluates Rohingya-related LULC change and its impact on elephant movement routes in Cox's Bazar.</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" s="10" t="inlineStr">
         <is>
           <t>P015</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R8" s="10" t="inlineStr">
         <is>
           <t>13 July 2026</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>Important for wildlife-corridor, connectivity and conservation-priority analysis.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>C008</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Chowdhury, 2025</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Land-Use Legacies and Tree Species Richness Affect Short-Term Resilience in Reforested Areas of the World's Largest Refugee Camp</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Chowdhury, F. I.; Bhuiyan, R. H.; Espelta, J. M.; Resco de Dios, V.; Dilshad, T.; Haque, M. R.; Aman, M. G.; Lloret, F.</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="10" t="n">
         <v>2025</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Ecological Engineering</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>10.1016/j.ecoleng.2025.107612</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>Hassan connection visible; additional connections to verify</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>To verify</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>Conservation and Restoration</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" s="10" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>Evaluates reforestation recovery and resilience in Kutupalong, supporting the restoration and conservation-priority component.</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" s="10" t="inlineStr">
         <is>
           <t>P016</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R9" s="10" t="inlineStr">
         <is>
           <t>13 July 2026</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>Restoration-focused rather than deforestation-attribution study.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>C009</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Liu, 2026</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Land-Use Governance of Borderland Protected Areas Under Refugee Expansion and Climate Threats: Evidence from Teknaf, Bangladesh</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Liu, J.; Zevenbergen, C.; Lu, J.; Qi, Q.; Veerbeek, W.; Chowdhury, S. W.; Qian, L.</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="10" t="n">
         <v>2026</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Land</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>10.3390/land15061024</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Multiple seed connections — exact connection unclear</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="10" t="inlineStr">
         <is>
           <t>Conservation and Restoration</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="10" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" s="10" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>Directly addresses land-use governance, protected areas, refugee expansion and climate pressure in Teknaf.</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" s="10" t="inlineStr">
         <is>
           <t>P017</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R10" s="10" t="inlineStr">
         <is>
           <t>13 July 2026</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>Very recent study; important for protected-area governance and policy recommendations.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="225" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>C010</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Sobczak-Szelc, 2026</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Exploring the Role of Common-Pool Resources and MalCoping in Socio-Environmental Dynamics: A Case Study of the Kutupalong Refugee Camp, Bangladesh</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Sobczak-Szelc, K.; Chułek, M.; Espegren, A.; Malak, M. A.; Jenerowicz-Sanikowska, M.; Quader, M. A.</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="10" t="n">
         <v>2026</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>Journal of Immigrant &amp;amp; Refugee Studies</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>10.1080/15562948.2025.2607538</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Sarkar connection visible; additional connections to verify</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>To verify</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="10" t="inlineStr">
         <is>
           <t>Background or Context</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" s="10" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>Provides qualitative evidence on common-pool resources, coping behaviour and socio-environmental pressures in Kutupalong, supporting interpretation of forest-loss drivers and policy responses.</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" s="10" t="inlineStr">
         <is>
           <t>P018</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R11" s="10" t="inlineStr">
         <is>
           <t>13 July 2026</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>Contextual and qualitative study; not a remote-sensing or causal forest-loss analysis. Verify final publication year during citation checking.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="180" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>C011</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Rashid, 2021</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Spatiotemporal changes of vegetation and land surface temperature in the refugee camps and its surrounding areas of Bangladesh after the Rohingya influx from Myanmar</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Rashid, K. J.; Hoque, M. A.; Esha, T. A.; Rahman, M. A.; Paul, A.</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="10" t="n">
         <v>2021</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Environment, Development and Sustainability</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>10.1007/s10668-020-00733-x</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>Already present in Litmap citation network</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="10" t="inlineStr">
         <is>
           <t>Direct Forest Change</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="10" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" s="10" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" s="10" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>Directly analyses post-influx vegetation and land-surface-temperature changes in the Rohingya camp landscape and surrounding areas.</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" s="10" t="inlineStr">
         <is>
           <t>P019</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R12" s="10" t="inlineStr">
         <is>
           <t>13 July 2026</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>Article was already present in the Litmap but had not been assigned a master-matrix ID. Online publication occurred in 2020; journal issue year retained as 2021.</t>
         </is>
@@ -4801,7 +6875,7 @@
     <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>P001 — Full-Text Extraction</t>
@@ -4827,7 +6901,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="45" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Verified citation</t>
@@ -4844,7 +6918,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Publication status</t>
@@ -4861,7 +6935,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Research objective</t>
@@ -4878,7 +6952,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Study area</t>
@@ -4912,7 +6986,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>NDVI dates</t>
@@ -4929,7 +7003,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Primary satellite data</t>
@@ -4946,7 +7020,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Reference and ancillary data</t>
@@ -4963,7 +7037,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Preprocessing</t>
@@ -4980,7 +7054,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Initial land-cover classes</t>
@@ -4997,7 +7071,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="45" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Predictors</t>
@@ -5014,7 +7088,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Random Forest settings</t>
@@ -5031,7 +7105,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Validation</t>
@@ -5048,7 +7122,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="45" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -5065,7 +7139,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Important variables</t>
@@ -5082,7 +7156,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Aggregate change</t>
@@ -5099,7 +7173,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Kutupalong–Balukhali</t>
@@ -5116,7 +7190,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Kutupalong conversion</t>
@@ -5133,7 +7207,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Nayapara–Leda</t>
@@ -5150,7 +7224,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Unchiprang</t>
@@ -5167,7 +7241,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>NDVI result</t>
@@ -5184,7 +7258,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="45" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Authors' interpretation</t>
@@ -5201,7 +7275,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="75" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Author-stated limitations</t>
@@ -5218,7 +7292,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="75" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Critical limitations for our study</t>
@@ -5235,7 +7309,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Relevance to proposed research</t>
@@ -5252,7 +7326,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>Research gap derived</t>
@@ -5269,7 +7343,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>How it will be cited</t>
@@ -5286,7 +7360,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Important figures/tables</t>
@@ -5303,7 +7377,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="30" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Direct quotations</t>
@@ -5354,7 +7428,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>Downloaded PDF</t>
@@ -5475,156 +7549,1325 @@
         </is>
       </c>
     </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DiD model</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Linear probability DiD with pixel and year FE (Eq. 1); continuous DiD for population/nightlights (Eq. 2)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>§5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Placebo tests</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Forest/settlement placebos for 2014 and 2017 (drop 2020); population/nightlights placebos for 2015 and 2016</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>§5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0–1 km exclusion test</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Omitting 0–1 km pixels reduces forest DiD from 7.6 pp to 4.5 pp (still significant)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>§5.3; Fig. 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Protected-area analysis</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Heterogeneity by protected vs non-protected pixels; losses concentrated outside protected areas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>§5.4; results</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Attributable forest loss</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>≈2,653.7 ha additional forest loss in 0–5 km treatment vs counterfactual; ~1,082.4 ha in 0–1 km and ~1,571.3 ha in 1–5 km</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>§6.2; fn. 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>District descriptive loss</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Forest/grassland −12,807.99 ha (−19.57%) from 2017 to 2020; camp-interior forest loss ≈1,337 ha</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Table 2; §6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Limitations</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Four LULC dates; one post year; 30 m Landsat; static buffers; possible spillover; no clustered SEs; appendices on request</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>§5–7; our appraisal</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Research gap</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>No annual long panel, time-varying exposure, SDID, fragmentation, carbon, XAI, or conservation-priority mapping</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Our appraisal</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Numerical inconsistency</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Settlement conversion narrative reports 7,681.9 ha then calculates 4,539.3 ha in footnote arithmetic</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>§6.2; fn. 15</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Extracted Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Paper ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10.1016/j.envc.2024.101063</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Fieldwork year</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2024 (Table 4); month/day not stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Restoration start</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2019; ~292 ha</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DiD model</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Linear probability DiD with pixel and year FE (Eq. 1); continuous DiD for population/nightlights (Eq. 2)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>§5.2</t>
+          <t>Damaged forest context</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>~3,200 ha reserved forest</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Placebo tests</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Forest/settlement placebos for 2014 and 2017 (drop 2020); population/nightlights placebos for 2015 and 2016</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>§5.2</t>
+          <t>Sampled blocks</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>34 (+2 controls)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0–1 km exclusion test</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Omitting 0–1 km pixels reduces forest DiD from 7.6 pp to 4.5 pp (still significant)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>§5.3; Fig. 7</t>
+          <t>Plot size</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10 m × 10 m; nested 1×1 m; root pit 0.5³ m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Protected-area analysis</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Heterogeneity by protected vs non-protected pixels; losses concentrated outside protected areas</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>§5.4; results</t>
+          <t>Mean AGB t/ha</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>33.34 ± 5.76</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Attributable forest loss</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>≈2,653.7 ha additional forest loss in 0–5 km treatment vs counterfactual; ~1,082.4 ha in 0–1 km and ~1,571.3 ha in 1–5 km</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>§6.2; fn. 14</t>
+          <t>Mean root BGB t/ha</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.26 ± 0.32</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>District descriptive loss</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Forest/grassland −12,807.99 ha (−19.57%) from 2017 to 2020; camp-interior forest loss ≈1,337 ha</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Table 2; §6.1</t>
+          <t>Mean total C t/ha</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>93.90 ± 4.85</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Four LULC dates; one post year; 30 m Landsat; static buffers; possible spillover; no clustered SEs; appendices on request</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>§5–7; our appraisal</t>
+          <t>Soil C to 30 cm t/ha</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>76.29 (abstract mean pool)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Research gap</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>No annual long panel, time-varying exposure, SDID, fragmentation, carbon, XAI, or conservation-priority mapping</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Our appraisal</t>
+          <t>AGB model</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ln(Y)=1.30+1.11 Ln(BA/ha); adj R² 0.98; Rmse 0.18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Numerical inconsistency</t>
+          <t>AGC model</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ln(Y)=0.61+1.11 Ln(BA/ha); adj R² 0.98; Rmse 0.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Research Gap</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>The study quantifies biomass and carbon stocks in restored sites, but does not estimate annual historical biomass loss, carbon loss from deforestation, CO2-equivalent emissions, spatially explicit carbon change, or the proportion causally attributable to the post-2017 refugee influx. The proposed research will integrate annual forest-loss maps with spatial biomass data and SDID estimates to quantify attributable above-ground carbon loss.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Extracted Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Paper ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10.1007/s11111-025-00489-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Image dates</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2016-11-30; 2024-01-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Study area</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>~2,500 ha; 34 camps</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Forest change ha</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1688.8 → 767.3 (−921.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Settlement change ha</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>144.8 → 1011.5 (+866.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Forest to settlement ha</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>695.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Total to settlement ha</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>919.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Forest NP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>663 → 2468</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Correlation r</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>−0.73 (p&lt;0.05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Camp 15 population</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>~57,922</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Camp 15 forest loss ha</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>~62.8–62.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>OA/Kappa 2016</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>97.6% / 0.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>OA/Kappa 2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>96.9% / 0.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Research Gap</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>P006 provides a detailed and recent camp-level assessment of LULC, fragmentation, NDVI and population distribution, but it remains a two-date descriptive comparison. The proposed research will extend this evidence through an annual 2001–2025 forest-loss and fragmentation panel, treatment and control landscapes beyond official camp boundaries, spatially robust validation, time-varying camp exposure, SDID causal attribution, above-ground carbon-loss estimation, SHAP-based driver interpretation and conservation-priority mapping.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="85" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Extracted Value</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Source/Section</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Paper ID</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>10.1257/aer.20190159</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AEA record</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Open full text</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>NBER Working Paper 25532, Revised July 2021</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Title page</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Main application</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>California Proposition 99; 39 states; 1970–2000; treated from 1989</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>§6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Panel requirements</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Balanced panel; binary treatment; pre/post periods</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>§2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Unit weights</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Reweight controls to match treated pre-treatment trajectories</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>§2; Algorithm 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Time weights</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Emphasize informative pre-treatment periods</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>§2; Algorithm 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Algorithm steps</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Regularization → unit weights → time weights → weighted DiD FE regression</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Algorithm 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>ζ = (N_tr T_post)^{1/4} σ̂</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>§2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Inference</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Bootstrap (Algorithm 2); jackknife (Algorithm 3); placebo inference</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>§5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Jackknife limit</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Not defined when N_treated = 1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>§5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Latent-factor model</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Interactive unit-by-time factors permitted in theory</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>§3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Software</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Settlement conversion narrative reports 7,681.9 ha then calculates 4,539.3 ha in footnote arithmetic</t>
+          <t>R package synthdid; vignette at synthinference.github.io/synthdid</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>§6.2; fn. 15</t>
+          <t>Title page</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Our provisional panel</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Grid cells; annual 2001–2025; pre 2001–2016; transition 2017; post 2018–2025</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Proposed design</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Benchmark models</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Conventional DiD; synthetic control; SDID</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Proposed design</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Required diagnostics</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Pre-fit plots; weight distributions; placebo areas/years; spillover checks</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Our appraisal</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Application limits</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Binary treatment; spatial spillover; classification error; continuous exposure</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Our appraisal</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="85" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Extracted Value</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Source/Section</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Paper ID</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Version date</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>11 November 2025</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Title page</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Pages</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>65 including technical appendix</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Publication status</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Working paper — under review; Peer Reviewed = No</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Author draft/CV</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>None verified</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Relation to P002</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Extension of earlier Dampha collaboration / WB WP 9948</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Acknowledgements</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Study area</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Cox’s Bazar + Naikhongchhari; Chittagong robustness</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Data/Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Land-cover period</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Feb 2016–Feb 2023; pre: 2016–2017; post: 2018–2023</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Dynamic World probabilities; upscaled 10 m → 30 m</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Initial sample</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>2,899,227 30 m grid cells</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Treatment</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>0–5 km from camp boundary</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>&gt;20 km; 5–20 km spillover zone omitted</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Matching</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>1 km grids; probit; NN K=1; caliper 0.1; common support</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Matched sample</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Control 347,561; Treatment 305,213 thirty-metre cells</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Event study</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Matched DiD; reference 2017; cell FE + year FE; SE at 1 km</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Forest 2019</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>−4.6 pp (~12% below baseline)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Abstract/Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Forest 2023</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Approximately −1.7 pp</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Settlement 2022–23</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Approximately +3.4 to +3.7 pp (~44% above baseline)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Protected areas</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Peak 2019 forest ~−3.2 pp; Himchari controls</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Heterogeneity</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Kutupalong</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>2019 forest ~−5.8; 2023 ~−2.1; settlement ~+4.6 to +4.8</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Heterogeneity</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Night lights</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>VIIRS 2013–2021; 2021 effect ~+0.2 (~4× baseline 0.05)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Mechanisms</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Biofuel extraction; LPG/fencing attenuation; GE settlement growth</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Discussion</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Causal method</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>PSM + DiD event study (not SDID)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Research gap</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Need longer panel, time-varying exposure, SDID, fragmentation, carbon</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Our appraisal</t>
         </is>
       </c>
     </row>
